--- a/Input/File_000.xlsx
+++ b/Input/File_000.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="24345" windowHeight="11805"/>
+    <workbookView windowWidth="23145" windowHeight="9675"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="1057">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="996">
   <si>
     <t>链接</t>
   </si>
@@ -44,33 +44,1830 @@
     <t>Screenshots</t>
   </si>
   <si>
+    <t>magnet:?xt=urn:btih:0022f4fd78b0cfeb0fb5e258d8695131e0e4bd30</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:005e1a46ce649ff9d864902bc13e82f38177196e</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0070df3803321c001ea82a5b5f08311f19dde3b7</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:007ea690cd76442339e6c3ee866599b70ed74afa</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0083ac9fed705e761b4565e88136c84c4d4534f9</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:00b19eb195da543d79bfe7aecf2fdd35919cf09b</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:00b71b72b51f96e16c1d8d07e34a56ff42b583ba</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:00e6630acd508efce45927913942da8ef22c6b23</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:00f2c68a326574af10a9dc89bd6686ee2bff0729</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0128f5a710ceb3384831b79f3829d061ac2ea595</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:014081a32c57f72aec36ab8acdab711702251a0b</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:015b3d2513f4fc7bbd03ec2ea1a039613f110202</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:01d13893ea3b1d6ce4ec84651f56f479d8771c6c</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:01dd62bff1a692019ff6e7f1bf9b7f908bdd0216</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:01fc0800b3cd20ce597eb71894a52a9705351ebc</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:020389cbf75cf8e1e0ffcb4a692b2418c12ee45b</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0210b42faedba103a73f5882871633a7742ba471</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0223578ff29c348eff9fd5224f6b5480a6f7e3ce</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:023cf41542241510d8eea2845d533eaed36d5eef</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:024e0bf9b58a3af78016de51190e78f2e074a859</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:025e521318d7bd3725a7c68dec60149fa12fc204</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0268f40a5228e78fd06b07186e335f166d8dc970</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:02bc27944279b7d2a91065d006d63c2bd44eb332</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:02f3e2322222f927dd582d122128514347478e23</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:02f976ad49b6c98f3b120b6b09b3c15611353677</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:03168be24ab5bd28229d926a2b5f70ebc578afec</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:03338bf9bbc1a3b50bd9e4caf6a82a44b2eab02f</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:033e00742f7ddeb5d85bed53e656e3184cf3227e</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:034e31b64cd5c7a52685ddf9cd03bc86aab44b3d</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0370aadc9a913f6cef9d3c6835cfc794dbefcd17</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:03be7c96fd3b558759b674f75e802240d940dba2</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0406a5b58ce363698b934efddaf858f093def615</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:042825b6ebac84b2d491a201af2e41154a7fab74</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:047352356cc0f78a8e7f26204ae74013bd0527be</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:048866cbe02b8bfcb8a1379a1a7716a4d046f603</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0492fc84509b8be145dda46a6654a9b208bba2de</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:04df81cbc831932cf09ff67f29aa3e313d0bc363</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:04eb3f0e993c8e18e3978c9d20b5e3ae017e667e</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:04fe15b15e7217b85c17a34b8393904e8710231e</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:05959cfd355f10c64058aa25cdc3173def7971d8</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:05bb15fa2414e81a43aa6cc8daba181d6a136e7d</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:05be6650930dc44244da9ff95aff38e489569268</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:05d3cc005ebce5da93b0bfd944e7e79a1285f198</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0633d4b8cddcbef337e9c749645e00dabe815127</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0635d9430084aa01edc4ddea5e8646010e5ca2a4</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0642112cb96239e3ddb7c9fb615ae3a2f52291f9</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:065337f73cdb8671e1aec0ba2c2d0a97c3dbe486</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:06d70a00e24b4981cf00755e183e5f17104788df</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:06e8b95b472cc866c2f6dbe94e94a7fcb0ca8765</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0704232f88478cd9968247049086aab94c9d31b6</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0744b67c4ce3077dc1b1f8dd35179cd2bfcdb979</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:076c8dd9276fdfe165a1f776b7785b21778366a0</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:07804285b615e4faf996d9403750720c43c2b01a</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:07bb7a585abfc78137900f72f163bd39284c7606</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:07f553f8442200f4e4a19675bfc3698bb52f1cef</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:082d2353069a2a16d8b00830febca425dc440d9e</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:084e7decf5220931613b8cf0d1f61815fd3f5e2a</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:086ccebbb9b9d17e43ca24dcb8ada5138ff96878</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:08a49b4f8c59c8e878ca93ba9ce57fe8d5c18852</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:08ae74cf35679162763b5994b05e71906df9ea86</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:08b8fd34f5f3df3a252aeeb1ad0e8ab614aa32d0</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0912b9d421a5dce44b5fa8716be1091f5afe0492</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0932f717a4469522d790640eff0635331e0c419f</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:09483e3a016488264ee3f1fedae8ac7451333bf6</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:09573e048348dee6a28a7d169542e53bd54cc0af</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0969e1a00e816e926f987ecb99b38f059657b1ad</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:09b9020cd5e81e0f998d02a717fd7f198fbf50be</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:09ceae5b84ecebc8db45f2b0f71adc507a7bafc8</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:09d20552f114f79f2deef467f8f4090db0e89333</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:09ee8185e3c664c7a6d30d1a83c0067317353b28</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:09eed306baf98d0a58c05fb6320f0c76131f5e84</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:09f0ec736e8af488a1cf40df706b29a248285c12</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0a4c3b01c3c66389db0b7884d41e4d1abb650f33</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0a51f89d3e293835155157cf9f9e12c5005d4396</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0a608acec5a7f68b129a1e563346eff84a4398cc</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0a63f03274f6d80c5ffe452a915531d86fc6fc98</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0a81538e1d5092fc84057d737ff31633c0b1857b</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0a9c926e8ced4fab8f1b9c6a754ae518579f14d2</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0aadadffaf0181378a538cb86a4f773398cd3091</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0abcac298c335d7a291c422beac07251a790bc3b</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0ad1bd126836f2b6be7c45f0d568acad209f0127</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0ad1e33c806c92a5ec17347aa7558bab0e71aa45</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0ae58f21e5f56727964056e03f1e1ea9c0e61ec7</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0b37810ec866e899d15818ac4f68a2880135cd9c</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0b8eeae0b1f790b25af6227aecdc412cd9329f87</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0ba38eff1c1810dafe45f943d0c0d5101551f1ad</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0bb5b1cfd7f71c0bf290fd5a03e0cd7603c24623</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0bbc16b1562839e2c9d8000008998ac6949a6f23</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0bc129a2117b5b9eb266266df13f7c892754f883</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0bef9c14f2639ce3742a3c660cf9028bf24e22ac</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0c16afd19ed718685ca87bb9656a879f1a15cb65</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0c302b0b807157791dd36f79056056c22253dbc4</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0c328baa77b2bed3e45619fab797a5d57664758d</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0c6abc76b8685f85a6d20a4e0b335c0153217c1b</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0c7b9d68a1e9fc4a2f67dbd214dc42ba8fec4997</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0c833b000d943c5634d33c5fed098a02fe3fa4e5</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0ca37652b005f83203686f08ad760914cbbc4d8f</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0caead9bc391e61f1c2fc24a5d1cf2c06b378251</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0caf811cc3fcda18f13cb65d383509512fd32282</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0cb877410b647de6dd904db41c6e62d2e1c38cf2</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0d28755d531ac86555bf9da348ddd8a7280199f2</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0d562ecc1b6ce629cc3c418dc45c3c200d4b3be0</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0dc4b852582702a133981fcc8033810eeab7302a</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0dcea6e87c651bdff7d7a55e23a758204e8b23d9</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0e2a6aee97bfd64f76a2fa20a0bdfa789c9824ba</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0e3afa3d130f020bf3c51d1aa6104ef984f1b0aa</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0e50e4fde700ec9da2dd58ab44d1999df6ddefb1</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0e573fc6e0b93540054630193851deb560100520</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0e68df905934d4c3617dfacbfa38e228bcaa3f00</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0e84be3e6907d08ae600a0b5e0c73c5d255535d0</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0ebc9b974efb974437d87fa3877d20d44ad67b3a</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0ebe564bc742d3b241943a3545aae8e0217017d4</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0ec2acf9e1f3a4194fd7f2979f624a40f9abe8f1</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0ed343cb2dc343c68b8e9496db52b77245ae4d85</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0edd315d218eb5fd2866ea194116361d85e0923a</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0f01025198558896a285621a9d8253cd02c4a4e5</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0f53a1354c10b1a6d9bf2d67ac85a436f03f7b43</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0f5963b9cb8fe8f2e319aaef45ad9d020544f1dc</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0f91e1e1b5e60e983874c900045d3c421d440b64</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0f986ee60a84b065a2a18e10088e77f53efa0610</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0f9bc39d02d2c9befe574f41bd0805c615ee7617</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0fa10cfebaea28eca45f42388a2d9d15bf0b73e8</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0fb41bb563de5933fefa8e7adaad54d3e9bb483f</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0fcfcae9e5d311de42451c0783dd274b7b71d810</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:1003fee38d17be8351ad808328cfbf63beb588b1</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:101c27c141c647c399606ba74d8d5a87fffae99d</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:103fdf30b18ccae3dc9200a2f0b6c5a8189a5aa2</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:104da3463e9478dae399cdae8e52eed459648f82</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:106b3fb918774409973272e26b06771d50b2fca1</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:107bbbdbd9a5db5ec35ee4cd64519e0ed53b6a8f</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:1081facce69e7bfe861e184f4225c34f445b910b</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:10db758f8221e731365c63d9c05007af3efdd33a</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:10dfd400d918c94d270cc26d21edde2eb148aed5</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:10ff4926d4dc5371166e5850322d1208a54ba587</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:1119069909e0d8231e22f3d4b882dc1996d1ea83</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:132d5ba95916efe0947afa145e9706654c17eafc</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:150cd32cab4ff2764a1d0b29164d7811a5c357f2</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:1516e3b07f2bc4f3fbcb62ba426861b4dd5ac9ce</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:15b71fe883d504a19b5bf959082dff9f84d1e721</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:16111b959898153cef3ea61a2cddf12ab2b8bade</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:16c8a0777873100e6e8450975f32996b4cf08f54</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:179ea8518ae7048c4a838b0b2abf0ad3444f7c69</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:17fa2db37cf7d1583e82318fba96fc235db575fd</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:191e7a47e210937236087187904c524e838270d5</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:195b2307e8188199c4fe1d81c595cc519de7535c</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:1b52970aa5bc36d748cb41407c2bc192711df581</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:1c5e840015279932e73d6bddb2b0c1aeddb2b3e4</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:1c88f8b262b2b9ed3fad708d3def1ae838495b64</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:1d95d91a34867febbe8b4026e7c8ee7e92d4b174</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:21f9acb1190a3b1dd48da7938de87463c10ad0f7</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2378bf11f2049d4f8180bea9195990031ed9bc0e</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:265e4b2470723996a968732f00e29dbe491bbf9f</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:26625128e935ce560b88233bdcb367f2becb06cb</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:269f532962e82f7f033fb5d13caff88789e2cecf</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:26a2bb308c7a164b80413cd83b3e723f6a9adf69</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:26b5e80399b75ce81a674b7ccffd1ae31ce694f4</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:26ef9f4297da334d763d63f24065f48fb723edb1</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:26f10d98dfd337c50462f665e6603091c30a55c9</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2710e82fdbadbd99e20b8883b65aee53981fef25</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:272e5aface0a3c61607e1b2fc9d81f59499cdc89</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2747436a22b61d0737a8abe403316344e2007abf</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:275614711c1680e6a6cc3f818c26931754101c83</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2766ed82e5637b4f4b958d05de4e48453e72d7a8</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:27a4a42eb36d183e5ebee5ee73a37796775bc5b8</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:27ab11ab48752011da373b4d027f4270e70ca001</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:27b37dcab66a44c71b662f185f1a6c567706a8a7</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:27e94881181fc05525aa567a606eee18835bbb83</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:280ca4788e226bb6ada4b8d609d9a36cd7bb9872</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:281713ecfe14a72cf8170a587a887a0d45774324</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:281cb88ea3c4cfceb14fa5d1d55aca2189c7465a</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2842e83c6978bf4c8b93665fd0c4db5f61c7c5bf</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2875ddf0127f5198e9bb8c9833bb658a2f109484</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:28b88841c7b50e6f053a700849f96e75450c8a1e</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:28bd1fe1ea477ed9bd8c66755250b3d945a5c0d3</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:28ecb19efaee90504f3540dd6ba6958a43a1a9fe</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:28f513228547a557fb25912dbf6ae2eaca553a0a</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:28fa2cc903c04d2b2cedb1ae2b54fb27bec9b75e</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2924dba94e220200a5f63d9d3ec8087b023e75a5</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:29745c41b214aa32aab9f0725e5dc543423cdb23</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2992323377dc4450df40d862ebac5736ac5908f2</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:299ae62afd80809d6addcda1a1e8ab58391f430f</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:299c74e7a8987b7e5583a6232e9921499f4a4950</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:29a9923601b5525982c06f20dd6a1181d0857bdd</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2a13acdd4ffed03ea1e9bc0dbb480c561f4d94d3</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2a13b1102419595bfc9f83389933a7897a49eaec</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2a25daf97898d7c70a9803a0e45defb2efd34953</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2a272caad02d80b8999ea25fafbf2adb4c170e16</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2a291ed458543ffcadcd6a211dad717f7db053f0</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2a2d3c09113e66f6f4e17b1c206e0c2859ae03db</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2a459151390ca988e7c02a369093bc13c6a05f9d</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2a56a349215f117543a5805302d41a6473889450</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2a6f9019a4946de25cad8ebeab817377cec88bd7</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2a700ee8034d4579fcce4484a1d8754d95558689</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2a7ffefcaab9114c1fc7c567eabb98a796f1c064</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2a86b113717d626d7c7999d9c0a32f9c8bd2757f</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2acccda5bf669e66f4b60dc2a59aa6ca8a08daa1</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2b025eb859bf2da3c8b992147e261e3384768d83</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2b0f1f4e2b1ff25cd60515fe55b690ee9dfbef83</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2b157b603793d949c450a9ee8e91d0c0124a4bc6</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2b1e48b389b7ab42e54ed8de2c7d06d9981e0c6e</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2b24759a952e2c9090bc8269e8370f63b9655434</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2b5c4622d1523e1c4b50a8c68e52abecf98a242f</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2b66aba812c846c251bcba4edd750cc91ff0195e</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2b9ae86e3b019711ae7d3f1908676b8d2e2743f0</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2bcdd210a5ba6c75e0b9b617bee722cd27158cc3</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2beeb2950b8edd998df0774cdfe379009ad92f3c</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2c385bb43839fb7044d1d6db5714cb1f99d04e20</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2c40b68dbb4aaa314e639ece76e747a01d92963f</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2ce0fa8fc53bed2fa597413af9a2146a29e06ee3</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2ce6b120675b7e1d262f34cc0be9b95815698c92</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2d0624ab8c1f3f216012173e6b8092cd9cff53fe</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2d26585fc592d87b7c74e0d9d4e591853bbb21db</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2d4b90318507de9d3d37fb4f00a0ade58b4d8316</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2d9ef73b7d497057d4122e58d532a0106cf7d2cd</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2de6197247bafe12bc4d9567321a14e8fe2cd694</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2de9a24defc87ea3f04ff49285bc966d6a631e05</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2e46a07125fae002bbbaf8b088f2aad706af54b2</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2e53402e6178768ab939fea2e5fe7e10bac64f89</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2e55a688919894fdeaec627e97631220f15079ea</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2ebfa0a11b91327cafcde1e79f41fb89583de9e0</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2edf5fb67444dafe4ddd842572e6ea4c48457ba5</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2f303d9692099bcabc4f9afd562317a2ef8f3768</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2f3378bc54b8990e322d9f089a4327d40044546d</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2f3ecb24cbc20d5597d15e0da835ecc7ca0ac81b</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2f529f7577ac6fb258efe8cc6c197676dbe9f8a4</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2f66730e379d4003e4fb3a496bf4b148f3e80300</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2fba16066c88d49ce2b057c1b0d51aa40955e20d</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:2fd1f9834de9773eafaa893dfc6e76665f6eaa92</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:30045968ff8830865c90952137aeca0f85bd15d1</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3057788fdd39eb14fbf581ef59442644b9f38361</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3099ca9b94ddd935b42abf69018ec5cea9473330</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:310e26463b6129d13b4bda260fa968b36a6b6e69</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:310f76f229c75d956b09181dcd849937f4c4e939</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:313ab87e6322212d316a4e28e5e04f7a38e0fa51</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:319e2203589731baab8ac2966f6b974492ac8990</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:31a2c4fadc48399d3f60954e646e3b71ade91085</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:31bf98cd45ca123e54d7ee9118ab48c86f151947</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:31c1d3cbc83b7a5c0698db5e7bba4355e17394da</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:31dd157cd4de9bc226cbca9c70b5b40fdd4ec4e9</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:321f506f86c09c3ea349742f7e1ef56f04cc4388</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:32209b33f29bc0a88a28ae98580956fa571285b1</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3257ab5b7c85e50884e6339c61ca1f5a9a266ff2</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:327cac9ce19c0f1d83f2dc46adddcdb9b72c75b3</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:327dbd4a35c2036bfe0ad719274994411e383546</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3289c9923215c782762ec9f2e872deebefe7477a</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:329e3c5d5a91997ac49afa02e4980b7f8f593169</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:32a23b9bf884e86969b7cfaaec047f92a7697574</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:32dea6679edaa76655222ba335305566fe196fe4</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:334f354cc2c4f69d81423b671bc41c04201041f3</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:33647a762a0f79a72e949c3b1d91410898c35060</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:33711be007f79433d40ea5342495b437368b18b0</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:33b5b0e8f9d063113ccb4985278da539f413b187</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:33c36905aee1c39df270c7f316ad76708cb9698d</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:344f5f7f52707434a9a536230ec576ae0dcb3259</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:348371086208d30b4210e34071fe82d5d4001d1c</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:34c4cd26b90d83203e3874da143febdfde031761</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:34c8f835be534c0a1e041cc95cde0bba4806a532</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:34e4feb8de16ff59994dbebf13489104bb92564e</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:35308769a7b66e60353f56e55e2ea3bc237a3b50</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3530f80d0eddf06cce6e5a93414c6b9e1f62337a</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:353ef0e48122a952edc7aafda03904f6a4f8ec0f</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:35866198fdd17999eff9382e21d0bdcbb5ee0361</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:359c79fc4e7960a6ff20b9e75491f2cb017d5f77</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:35adff49eb33e0e194c568e3fbf226061fbcd910</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:35b2c217bed242b304f4d29743ea84406f07571f</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:35b5d0206d908042034ec743c8dce814018c193d</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:35f1c3564b4108d4e43f081927f3360fa84ed13a</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3602929ad0ddd9f69a8a79cf7dee77e3f49fe091</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3615fdf64ecc1b834cf312b4d5d4ccc90f2f0004</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3626f4e1d97670ad23e7f5366c140a837344c588</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3657fc474ba25a41538f989cb3b2a2680288f2f9</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3676bd1eee01c1fb22ff11a7f3484a6cc444f688</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:367fc91c2d1965509a1b762f408f3164060bbd40</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:36811ded304b033d4fa872f1703f8b97b6deef3c</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:368ea7b65f89339253da4d7d752316cb68b82769</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:373217b785617982237ad84743287e94574f6709</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:37400da692adc40e6445360dd39cb23b45e0f724</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3771568d71997f5eaf2b4e9da0187679e6559b7c</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3772231f02eb0a3fa4369add00efd61418e7657f</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:37795d8da3e24400b3b76d1219f6d2cfe4f77064</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:37ccd91da5439a5dcd0b3380874ce91e11f676dd</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:380e301f739101860585f57511c9ce6e234ba7d6</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:381008518531f686350689426c3a53e258bc74ae</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3812ebee7693c2da4bc582dffc0260d66765378e</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:381f1a69017c83bdb8e97b6fe127d88e4786a782</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3837597298a2036d724c86e6e268b3149b4ffdc3</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:385df497fd6c4fc0a110ea037878b37371654c7c</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:385edf16fb91f53f82cfbeea88343b509357e7a3</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3867dff8dad4b8c32eb14177d5d43c09fa75679d</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:389ed1c1db2a49faab71c2487b9d0aa8e153f5dd</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:38bca2173265e59296e67ca0f15351533e7a8538</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:38d6d35670af52d151bb894e88dd0cf0e8b95fe5</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:39911dabb9996cf3a964a6f86b9cb41e227f0490</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:39b1062efcc089909704f238d7dc4e55fe1b0f4f</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:39d05c10c7c4b839b50601c1fff85a8a5ce15538</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:39f21b69486a8020a4525746fb0123198f7cf588</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3a304a3e0c8aa200ef8cd6ceda3d1b438440c5e8</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3a377a784035073ca5878456e58aaf11004943d8</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3a3f522e18f124fb8cac7ad3e2e34f3c3700d18d</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3a620c8f466d217da42990425b82b6102c2ebbbb</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3a7c53a10d1b3cb756b4c04a27cbdc381f113dd6</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3a9950d18039578aa47a45bce600433cf6bc2460</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3abf5f4b6d0e6836b4b1cca30cc30e22e09a662b</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3afb161dc63c30719299277ea5ca4655a7d5ca5a</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3afca03fad4d8db8fc48f92e5a902ddd3bf48bc6</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3b21adad00dd4c119301251225510e60a11d5ce6</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3bccd9072e854a527b99559015d225c6574ac65e</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3bcf10784a3d9a68bda8b3bae50c5f25ad0b7f7a</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3bd4048ce69e6190f978507d0731c1d209d39914</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3bdd3650c63f8c4ef16086f5ae0db89301879e8c</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3bea24fa1131f5cdbd23d13e2004f2ba34da6479</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3bf1a428822de7e12ca5e9e4426cbabed12fa53f</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3c0e4f62e4a8f173a31c219c72911e7cf714a2ae</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3c1260f309ba1d7bda277e6ac9f41d268edcd361</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3c3952bb88f69afbd8dbb7fb07b2d2d22b46436d</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3c4aaf96ee364863d855451dfbfda38992362e02</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3c8013e00e861f06c9f07e698ccddc58f8515abf</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3cccd8a10aa858e2bea076eeae90ddb1932092b3</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3cdbb0e4cae8949514dd32e517c9c9a04927b5f2</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3d185e21717268d9019fe5a0c6dda79a39116a38</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3d25efc978e327a15e7812ae587205b4d5cbb0aa</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3d360088bcc9a40f2741a61b3a6f8e62b3e2a339</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3d4a7bc3ecb8fd6f3f4ffec37642ca0ecd49917c</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3d6899bfd3896ac4bf8411285e3bc017b524c287</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3e1ff29e4148e5a1e6cfd85ad434f20b8c6e9f23</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3e500c3b42eb36e9fbdb24c83c2c52831cbdf04b</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3e8820608a8765cb835027416456fc418036c878</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3f06022952ec30181708086cfc6bee87e3107864</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3f2b940f9bee594cc215d70aa46af17a8427bdf9</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3f478b9b5533f4fc0c95edfb3bd56a059505477b</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3f487516399a8062ce295be08ce5af9ec7bec940</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3fae88685849b17207ab9939b207a6aad5daaf17</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3fcb639ee221dff21b57f4eb50a5d401d482bf7b</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:3feedbc7dd44b821aa558f9c122c612ba16d15aa</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4050143600e2f97086d2bd7efa9cc9f3c8e87186</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:406df4a09e836a3c9f4425417add44d8c5b152ed</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:40710c24dbfa09447d45952236bf3a799a0c3080</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:40858d86a00a683cf53ba639c9dc9795efed6d9c</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:40bd6a69c04b8a318a9ea70b426e283a40d3d382</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:40c92d9769624fa43bf759e5c58d5732dc748e1e</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:40c9d241c5c051b388325401cc8626ca60915b42</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:412e811294c357dc28000ec5cc6ea54d91f8f8df</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4162167576eb38e65b8fe25d5d71430bae1c2bad</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:41ff32a03e45bc510bcd91405257fe844c8e74b7</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:420971b77d66d2244047fe8c6907d2da60eafb2f</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:420fd69f848c623d7510cc1bda13439f1c378db5</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4246f9f6ae42d769703d2fa2952c89d61b25547d</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:425a6ecdac967d4c959fd306daf2465062c183ce</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:42aa15864078b8f2d2498e336c935ecc0994d79e</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:42b0f8b865a504ef1882a9aeb3c37ec4b77fba86</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:430265cb535d50f77fbeb943cbbbada475c80c06</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:430892547f924c9a1241c264c452a75fa1a72466</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4350cff0f29da39ce7025b0c748bede385ab0f2c</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:441b6b05f9244782ccb215a6d3185b3657d4a390</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:443d2498cd6720224920abfb7e71e5a1796a3354</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:44526ec90b6086e1c74fb2a9c435c440adaaa30e</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:44552a61a91a45f174b41d21662ed11001a30caa</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4468c84181640b6aa8157ec79001f1e95973fcec</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:447c58142a8f62bea4d16d2d1ccd4af944675599</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4484c6b21b9f60f489d41cf90ee859e9b54ba63c</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4486bb109cf2e1975a060ad92110fbe356e900eb</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:449d2891a711a34791392f1de295481d103d46e9</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:44a9eaed443d7379bbbc4acdb172795ce9b71cb8</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:44ef3ac03f6662b4f3fa12f6e410fd7756acd3aa</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4550163ff4454a5d316ff16e6c63479efff977fa</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:455676da549e42cf23d3832eb510c0fe93a5d302</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:455eb4cf6986dda4628d318476eec0374c96eb20</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4566d46f782bf279acb8b04eccbc6a783bfd6253</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:456f7325ea2d5f470a26c26862adfb15acdb2e14</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4575df327eabcf3ba5c902d49ea5e5302b327b85</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:457da8744c5ed035a423fdf4d333e4b7caca70ef</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:45b2720a76b148af0c2e2844ca611f7cca7d17fa</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:45e1c102d18c5167fd745d126e1e43fbbaf50890</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:45f2355fe5d763d2b352d22c98754918a38fbe11</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4622498768ffbd024c038a8510dff07e8ba628bf</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4641fd40554b7b69580cd013684ad859ca4e0b11</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:466f0431792e0da5a97343606ead0b9acd8afa01</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:46723468b4ac5d41b88b59a6aa1f736004772209</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:46779a38ab50f204319b773c403fdad886332e2f</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:467bceab5441d7c875c1623a19b942a5194964c5</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:469004e580d626028ac6a2ec9f5321da6bd5c8fc</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:469892c579d806dd122dd327bc7c0f2f4a2ad76e</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:46adc64fd278797edd55a622e3f386ec2b24f35f</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4709b407fb0bcbc9fb07e178b1769db11b127a2d</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4726befc4be4b6061913fea17431ce04e19ba1a2</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:472b41b872a65685b315af9a2aa34bc4ba244880</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:473891f84fcd6bfa8e2c3399713e20715bc6ce24</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:47738032773165d2c4a75a5cc687ee960e83912a</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:478b889f63a8868f173d8f5663baa0b84d07914f</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:47ac0e3a00f2705a44a7e3d08b25b0c1fb489a32</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:47ca66153f08ccd82ac9d0fb57ae841152151c9b</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:47cf435a57043b9e064c0d0be2429912e56ed4e0</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:47d36b854a178435c9751ba48e718dc12c5bb353</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4819c04224b1bb704e2a42402cf98b88c4316d21</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:48271ebdbafc3928c537ac9dd57add797c37bd30</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4833b57bd5bcd046192b7b1452ebaa054479a61e</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4850cf1467a2755c26ca3a26b69ba5135bd5e7bd</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4877ab43888dc2584fd85788b6b656aac6228a5d</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:488d5d23f0316189c75903ef8b28bca7ade319d9</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:48a1ff5c72cd6d24990e624e424bffa5dac9a39b</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:48dc7a4fb3a1a6974214040b4d88e64c9c755450</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4900e60da18a664f5b6fb90af1cd3c2f8cf5233c</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4904be0062046e14ee694074b2e98058ea4673c9</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:491285cc1b46d784e183f822e5cc0d576d83dcd5</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:495f45554ea74e8df1a17dbbb263b4e96b8b58ce</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:49d3650015f1772778f6f37ffa2e25fcf1ffbe66</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:49f93c56314b599a02f5e3ad956b9fe756a1f0d6</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:49fd4aad94400bcd112cf947f91a43802c3db7ed</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4a12d6cc2306d7eef6b105826a1a2323b536c1a2</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4a2b4c1bd2ce5f03627440ce32f4878d2ce43169</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4a33a88c5f078b7a997d2b32a260610f285067b0</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4a617e9657c3110887285449f37665627556f540</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4a8df1fbcf06dc53a5aa7296a0b12966d9c8f3a0</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4a92cd8534b3bd709f815894e035724612edc4ec</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4a99eef0d4c71e97677ea5a27120ac0973394eb0</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4aad64e1d0ea7e6a6c1919845788fad7a9adc0e9</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4acd5d22b2e6bdb4861cc35d63d9adff79c34b3b</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4b092c7bf475e0d9b07e13f9aea9972350d9631d</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4b241fed126308bbcb8be32a98ada04988bf7338</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4b3e8c3d5e806e3fa8956a13875a9f7d1277107b</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4b5de02993751e090c2195dd400e71c0559fd630</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4b76e99ccc575c0abea96bbf8c024ac97900b5f3</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4b81849fe74f329792d1c6baa91b9c6df3592fa1</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4ca4525871615da04d73ab2b4191533289831a7c</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4cc0be19724aa83e8061a376ef0aa6a379ac80f5</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4d59152475ca00baf3d76b2087c9baca7f4b1676</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4d69dd586d8ee7f8d0248fe19bf24579bb299eaf</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4d92d011673ffd1b62974c2e0fc69ef651584155</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4d97ff71af720e4fd59b4956d200036f95f57c5a</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4de37babadb83d8886287c30fbd754668cdf79ac</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4e15266853eb8ce16a4b8116ebe42ab8a1c9b986</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4e5ce3c2797ef4835cdf335e3e7bda962a878e6c</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4e68d188e0a1c189dbe80baa4c6e1316c07d342b</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4e6d3f811fa8080e4aedb645bbaf66de062cac59</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4ea299bc745121e8710803cccebcb9a6363f9829</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4eb13bca4ca0db985659a1a1bf785b69e88c0390</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4ee896b13e6c7160c4422564c91533157fc30e2c</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4eebd096a05143474fd43e34e51d1fcfc4843480</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4f099789dc342133a6a30bf4cb949b9df7680de2</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4f471a1a02d40cd7e3261055af5075490f7d18e9</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4f7b6791f49e7ac9eaf4584442ad3f4dde8e4a97</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4f987fbf332662b34159876d6fdf665d54b6e93a</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:4ff404e1ae80a05dd936bdf61d085275067a0e62</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5006581550ba669f0dca45cf001d353017da4d35</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:501448b278545b10c5aeedcc352d3872f24b6d36</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:505e91f0d3c95b850f4096932e6d3d80a7ae5422</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:506dd018f1ad37d092cabe6d183bd191a7ba104b</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:50833bc0dfbf04b37b08618cc2f36e176386ecc5</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5085b45d9bbe2c0017058981a0a9621c7bb485b8</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5087f57f3d7239dec57d8b12ed384205cf586b37</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:509bd98eac24a3fae51278b49e06c16f84505875</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:50b081379c9ab95000721b085a70dd4852e6362a</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:50d1b19753574c6a42522f56546a7dab9cd4be85</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:50e45d785e9e7c6308a5d263df160db8d3ffd9a2</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:510c24c86978cb9c2b4c07f09fa5d4d4e6734e65</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:510c38251b3358151fc4b833ce4477338a0a5ecb</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:510ee7b19d52689d3d972251834d406d26afc14d</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5113158c8b21d5fab06345f2d93c605376036701</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:513ae9870788e5b490869dc910e9622b6628318d</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:519724b4e2fe77195ad4398683dcf71f17d24e1f</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:519acafa0aca69fceb6c0108b12a3152617e480b</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:51b5315f78f0d3203894cca9cb034c5ec9828dc8</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:51ed8a7961914ee25880e685a61477ebb57aa456</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:51f3abf0587c808eeb11f3c0abeb443ca97ad198</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:522edd9df0ead16d7ad89a0cf84ef9e009d2a551</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:526f15f0902e746514c7da8b1eee56e9f583ccc7</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5283137c9d4c4ba32aba7d87a6bc2f531308fe64</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:52b3a34b6be32f3d7209fc8c2678e905825a53f1</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:52e9250e4f628c1b74b56505c2f1cf1c467e5f83</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:52f9576ca3440e101e498be4f768197cf9a96dbf</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5302423800f33b4e05b09c4272d0f9dcac3da1c0</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:533713de520ba43ec6191b15a1c52269f14906fe</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:533ace2bffc61206643bc15ee652895c3987985e</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:53578b888001271bd428433afb5ab0f923c8aa12</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5363dd3b52a5d8f0f7a7d203a4983c53c97c9127</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:536f385c431a59c80d105d6fb8024eaa90069328</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5394a82a3347d3ce7f502917e01997ad98f92d38</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:53a6f3938d84d975bb12e853298c6eaf7662369b</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:53b0531aa9002799bb706f2214b0d20a0d26bdcc</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:540c3bac4a5d994df7c78199b27f95e051009f43</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:541f54010b91ed27bf8055e52fbf88114951baeb</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:54222e70e9f7f1cc6c42b128d05de1e6be3c45df</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:54489791bda279421ce164cae3e4ac96a94d3434</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:546964dc024fe412672b54e11bea086033a97bfc</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:548e64bd421864cb0e85c5e8c81077d16b41646a</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5492ab8c0e9debcb5a9f06302f9b7d66579f3173</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:54b764262e5d7f0bb73d07de63fafdd889c92efb</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:54d3d8fee9ceae883a1913f5290a28dd4e4375af</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5500f0a3ba61011abd584c8df66cf13888ddb0bf</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5508187f440482f942bc712187eadf53729c2a81</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5517640c56d6e8d8ba65550e7af417793005d168</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:559a387e201d038204db191460ba5dc4fa84b53e</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5636b0cd30b5a6a611bfa4aa209bbd19e7b3d5bd</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5640e350c0f52db6d16170b9a7c6c29477473b05</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:568f66a4afda15bf1f08d000c47feb567555c9c4</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5691a839f50672ebc3269b259221050656cae644</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:56d527c652d2b1535408f3073cb3438b14425981</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:56dece437eac567fe000d8c8b45b35f52816891f</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5757479b4b410d228fbe873557dbe08128690ea2</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:57792aca07eee28bbc2ea66f07235d85e4219317</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:57a582305734b95be93976465bf1ea3b849d6d75</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:57bbeaf3942118aaff8b7228b3ee63387f460318</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:57f4df3bee06f1eb41ae6cd0e202505a09abd25e</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:57fe26e62bd5c3195ac587d67c32d86dbf215153</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:582e8683bf1c44cf6b83c3cf8bb38a75b9e29356</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:58302fa635bf85323c000825b4e520349d5ece5f</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:585c46051e7c529ecf76dceee7524fb0bf46e56e</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5886cdb9b61040c01617b9790bc40d19f34b679d</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:58abd8287f897ee8c152b4deb518ff78a3b80fea</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:592bac122164bcd114b890c4b03332a6b17f6e8f</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:596e55c581f7f715a38c9164c55338b30ae17802</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5970b70b93261f4a875dffb4f783b6eb369f6906</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5970c1e78be1e5b7e888860633997938b949c447</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:59793c851b94cb6371a09b7d6f0aa1c9e57ff74f</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:598bb35fdcfb03e2591a9a4d54b1a74996adf54c</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5990a591330a7f4ec30a61d405e641241802b940</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:599a4b2475966c592f823fc2e07ee1a1272f6c2b</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:59a5ce0c414d51824568c8e0dbf4fd815f61da0d</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:59d46454c43a73e7b6e624df7531010a77b5b6ba</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:59de0f98cf65ef7e9577062f62859351ce210b2b</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:59e0d9342ed7c5898cbce7d3932837332548c635</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:59e4537733fd09189d90edace74102204ffd356b</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:59e5addd5c52e6ca0e3da115c802da6acb9be84c</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:59f1c2add4a011054b3138cb7e3394f0d06afc79</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5a0b02e466008609459b47a86718ae67540ce24d</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5a4dc3400bba3a871831c8ae80acf2bc60a0343a</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5a54a2ac47bbfa6490d5c2dfd6eea74ab45a81c1</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5a8495e0fcf4d25fbce3e9651f7933c535332538</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5aa779d8cf42d8216a2a0919ded426833956d2b6</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5aca700c2b451fbb9472864f52aa79f3fa191aab</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5ad5435732ecacddb163944bdb29bc8793e9cb04</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5b10d3f94ebc084e4aa46c0446b03099017b7e19</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5b20255c5ea588afc7262246081d53d1d3151bec</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5b30d4ed752c0c4d2b221858b72bfd9e9f643701</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5c0735c692fde1e42b7c40b187328d11e57a42b3</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5c13a906131ee9a01ff0eb209a5e58f78bd05fa9</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5c1a42cb0ee077554ed267e0dd5070b65c7376ec</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5c36d8dbd682d270859dd5015585a89361b60470</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5c67cd8001a0fa53e91d6802b43a71a229559d39</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5c6d19fd23030dbcac5c65180f73c3fc88b9e9eb</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5c79e96c1c3c59553f1693118db44bc063d750a4</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5c7a8ebae1dd2a8ee53bbbd24da7889d98eed00a</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5cb74030eb130c302efd8780a3f852e301397a25</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5ceb81641b862d0801e821b5611e9044608830b7</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5d0258f18787d49971136dfbf87e2d500f910a20</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5d86c7f4f3228c1b6c8cc60afde8e58e13792c86</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5e32729600b04de8e729739641c19577b353be16</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5e6f653b9312b437d4460087be03eafd91685b9b</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5ee97b3b01910d2cedb3fd2f16139efb5b771ffa</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5ef1847f99aba5e7b7d9ee4a2bbd5cf3652b5bb1</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5f1524b00ce1659cab1c53c011575a461a68a20c</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:5ff9d1b438e4cfe60ffea7e95736d0dc2f3cd006</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:61371e1354febbe07a14128332c593764d637fae</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:61d4197b65439a91675cee6190ef1569e976a954</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:61e046244ec33e4f2488e5913fcff1d7db526e52</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:6264ed7eb7b3138137e1af85dc2d3a6429eab672</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:62a9f6bd188deb6943a661e864c9b94a7fbd77a7</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:62e96a41018ecc2379f3fdd5a1417a0078040e01</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:64b250dce83b4134c62cf37c1034a633c79423b2</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:64e1e31a32f634363265f4d3842a8c2828b12371</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:653659a8a999d8b91233d24b4a8cee7326f67154</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:65a78654c73d43023bb23e06f6ce9df9bf4e7bd7</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:669e67dfa1ad6e73ff83c27ff9dc87258e72fb8a</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:678ab547730d7e179d02871ef7a05aa2bd9547a7</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:67bc320d632d3b0df83e308f9f3f6725aa6d9306</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:68ec50623929d1e305e2fa1caa1d9bda5b05ec27</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:6901b51822193eabef55e2911522eb1751652dc5</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:6abed1e8a7a058a2fc8071a9bbbada40b065791e</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:6af90699d0659c3e71755d1a54b140d030db9af1</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:6b4f8cd210f474a80187df8105ee136ee1e6bc86</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:6b86e7b9877b11695ab0b1bb5b4a7c7b2a14b833</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:6b8eb3db398e37682133facbebefee232f617176</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:6ebc7a8cfaf62d764918dafa5a4f065265c1a02a</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:7065d3b859351d62e3c35e0f93bbfaf23fb516ec</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:70e21feffface22e553da1b1ea1367360474373d</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:722a72422ac35dcbd216afb8c632fc131d996cfa</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:7299f613dc5a9082d56ed8489aed0700f8806253</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:729f92a17dd2644633f475a09997c0afaa661207</t>
+  </si>
+  <si>
     <t>magnet:?xt=urn:btih:72f9a347809947144fc1e4c8f07699c926fdcdd9</t>
   </si>
   <si>
+    <t>magnet:?xt=urn:btih:738a229c755e8ec0f528cbdd3c1b7dc81086b4e3</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:73ff4cbcb967d26effb7414e1a09a40a9fb1fd42</t>
+  </si>
+  <si>
     <t>magnet:?xt=urn:btih:7413745443c0da2a855b5ab85a7396613a349140</t>
   </si>
   <si>
+    <t>magnet:?xt=urn:btih:741f62ed726942bb1b908924157b5ce8cf8dc0c6</t>
+  </si>
+  <si>
     <t>magnet:?xt=urn:btih:742301b8eb3cb5a83b75872cada5ab6b0759df1f</t>
   </si>
   <si>
+    <t>magnet:?xt=urn:btih:744148b85dd0e688c0a95350bcdf590135a5941c</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:744527bb200c04bb60f877fd4eb894f06b89e309</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:74551308f72025fdbef6be96b623b4a3163de13e</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:74be276bd77f1d620be630bc100e1fa9f081b67f</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:76c83d31a76321194386a9f6188ad1753f175078</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:7725dfba00e1d2555d71d6f5a76179a5bf678848</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:785c761a3aebab3311728c9d588cc4b6801c4a24</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:78f983a60bc0dd899151a94fa38cf50e3887168d</t>
+  </si>
+  <si>
     <t>magnet:?xt=urn:btih:79a1f3ae7ebaa0ca2ff946177129244d776af806</t>
   </si>
   <si>
+    <t>magnet:?xt=urn:btih:79b8fa0bc9b6e04d9c8ac0d95e5c3fb362d9cec7</t>
+  </si>
+  <si>
     <t>magnet:?xt=urn:btih:7a866986f4dba4bbada716a2e643aa0bfb7e7907</t>
   </si>
   <si>
+    <t>magnet:?xt=urn:btih:7a945bda5595f8a98a9f5da688ba9cc2abe2fcb6</t>
+  </si>
+  <si>
     <t>magnet:?xt=urn:btih:7b22516d37c30394c78a037a7ee01f1b8a19a292</t>
   </si>
   <si>
+    <t>magnet:?xt=urn:btih:7b29314957053e8cbcaa4b33ec3bea95d8ee68bf</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:7be9e1c0e6574a1890985d14a42cf6e33072e1e6</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:7c3d6b4610dc7da7fc0d59ed8c4c50d5ff412bce</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:7d62658354b2fdb4063db68a801f4793d4acd858</t>
+  </si>
+  <si>
     <t>magnet:?xt=urn:btih:7da64b57a37959517c86413b1161bba385178635</t>
   </si>
   <si>
     <t>magnet:?xt=urn:btih:7e14542d8b3fc889186b82cbba145e67acdbb2c6</t>
   </si>
   <si>
+    <t>magnet:?xt=urn:btih:7e2f013af1de67a229ce0ffbee376c198837e5f7</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:7e305dbace575bc641f906a84fbf9b563608e411</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:7ed55d027d6817c6df46e09dcacc64ac1680bbf0</t>
+  </si>
+  <si>
     <t>magnet:?xt=urn:btih:7f007b5ee2645c581792bf901c2054ce14f87a24</t>
   </si>
   <si>
+    <t>magnet:?xt=urn:btih:80e45fc578a8ab3d75b2aaa5a91f5c43fe953876</t>
+  </si>
+  <si>
     <t>magnet:?xt=urn:btih:810fdf600c65e12bf4fc27d7f322884fbde54d5a</t>
   </si>
   <si>
@@ -80,6 +1877,9 @@
     <t>magnet:?xt=urn:btih:81598bf63a6e3d56e8298557bce3711034acd909</t>
   </si>
   <si>
+    <t>magnet:?xt=urn:btih:82bc2667ded162bd2c04b26935d46ffa5f54c4f0</t>
+  </si>
+  <si>
     <t>magnet:?xt=urn:btih:83f4a173e6e9def000c06935c399101809adb4d4</t>
   </si>
   <si>
@@ -89,21 +1889,39 @@
     <t>magnet:?xt=urn:btih:84ca98a701ab9c9b9889fa5d972f096a703829ad</t>
   </si>
   <si>
+    <t>magnet:?xt=urn:btih:8571ed1d595069b7c8679cd4171124d8b98ddf26</t>
+  </si>
+  <si>
     <t>magnet:?xt=urn:btih:858607d4b7ed0c4fc7847a062e1bf3b5025e0317</t>
   </si>
   <si>
+    <t>magnet:?xt=urn:btih:85c6fcd29109445a6f114a461098f6fc0fd7e423</t>
+  </si>
+  <si>
     <t>magnet:?xt=urn:btih:866a910f1f3201bfb52e368eec2514ba608f3412</t>
   </si>
   <si>
+    <t>magnet:?xt=urn:btih:86961ba39226da222965e637077458419966479a</t>
+  </si>
+  <si>
     <t>magnet:?xt=urn:btih:86ad2075c7da54dd8bcae46e77e2fd480c920087</t>
   </si>
   <si>
+    <t>magnet:?xt=urn:btih:86d5834311dadd713e2522ecd18283d607630b92</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:874869e2959732c58b27bcedbcc1933390ec6f4a</t>
+  </si>
+  <si>
     <t>magnet:?xt=urn:btih:879c13a769fcca9e9524f909e789622694d2a99a</t>
   </si>
   <si>
     <t>magnet:?xt=urn:btih:87ce23ba9e32a6ad1d18cac631a92ec69d44d7b7</t>
   </si>
   <si>
+    <t>magnet:?xt=urn:btih:885c78862362422f532255dd8eafba47f46adcc7</t>
+  </si>
+  <si>
     <t>magnet:?xt=urn:btih:88608b23397627aa0a7b21b12f7d52427fce53c3</t>
   </si>
   <si>
@@ -113,15 +1931,45 @@
     <t>magnet:?xt=urn:btih:89339dc38c7cd2ffbf09d72091b98288af3abe6d</t>
   </si>
   <si>
+    <t>magnet:?xt=urn:btih:895c7a2ae27a0c45de1ae7c425231d0eddc55d70</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:8af2a45f1f9a8b5cd9bfa8765c31fbd5343e19c8</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:8b2882958240b43f5a67bfc90f8cf65f090fac09</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:8cac5dc61d12d7dfd1b5329489d3597fb938459f</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:8d0fd33ab26eec67772d93efa74a52efcf21dd2c</t>
+  </si>
+  <si>
     <t>magnet:?xt=urn:btih:8d689665e867166dc9794941673781068d84e0d9</t>
   </si>
   <si>
+    <t>magnet:?xt=urn:btih:8d95bfeb6d4e5f232f202bdfab8f06ec11209c26</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:8dddf6722e920ef47d96ac0756a3872fa9ac8d9b</t>
+  </si>
+  <si>
     <t>magnet:?xt=urn:btih:8e3848cfe8a85fadb652cc77cafa9c9cd0f2ddb8</t>
   </si>
   <si>
+    <t>magnet:?xt=urn:btih:8ec22bb584565f0b7bb6dabf556a4117b8d3a161</t>
+  </si>
+  <si>
     <t>magnet:?xt=urn:btih:8efb794392f4ede43838616d9638aa65bfda248d</t>
   </si>
   <si>
+    <t>magnet:?xt=urn:btih:9029c9ebf8c3c71ab5709c5c1296cd81dbd1143c</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:90fbe96322368351d8d6e6708a8fbdebc867fa93</t>
+  </si>
+  <si>
     <t>magnet:?xt=urn:btih:91189a5e850489f7684de06f5bdbb072d390456a</t>
   </si>
   <si>
@@ -134,33 +1982,66 @@
     <t>magnet:?xt=urn:btih:930b35ab138e9a3649068004cfb06d2805856f5f</t>
   </si>
   <si>
+    <t>magnet:?xt=urn:btih:945be7b6b063c65bc7ff0825d9f62d34b9a2c58b</t>
+  </si>
+  <si>
     <t>magnet:?xt=urn:btih:961e5cfc5bc518f08704dcfbbb72c3e9b8c48229</t>
   </si>
   <si>
+    <t>magnet:?xt=urn:btih:966852a8196e1c58c39a7192ce4556fd31e66b8b</t>
+  </si>
+  <si>
     <t>magnet:?xt=urn:btih:981e5cd6c49c05ee3c064e1176174f6dfa573bdd</t>
   </si>
   <si>
     <t>magnet:?xt=urn:btih:9941f76456bfaf8794c61fedff698753fbff922d</t>
   </si>
   <si>
+    <t>magnet:?xt=urn:btih:99a9100f4bef6c87ae843ebd77a511da9d1469ec</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:99cfd0bab948e7842cf3750022bfbc17690f782e</t>
+  </si>
+  <si>
     <t>magnet:?xt=urn:btih:9a40342cbe227fe2186b1b8b98b62609978f58df</t>
   </si>
   <si>
     <t>magnet:?xt=urn:btih:9a98befb891d4af5f91fdfd429c6cd6374f5c893</t>
   </si>
   <si>
+    <t>magnet:?xt=urn:btih:9aa82cdd8884999817776a4ad7f69d40fd3b7411</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:9aca7914823794e2790e37302e9aad2b62986db2</t>
+  </si>
+  <si>
     <t>magnet:?xt=urn:btih:9adecc81c5b48ab404c67df1581341869e7a7eed</t>
   </si>
   <si>
+    <t>magnet:?xt=urn:btih:9af59e31580b0dedcbab79e8065e77b68bf61741</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:9bac98d0062eb28e9233f2a1f3b85346b487588f</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:9c99f25381a03bf2c5c04bb3f1ff8e5b774c4d95</t>
+  </si>
+  <si>
     <t>magnet:?xt=urn:btih:9cd5bd9c643b7b806f7f2caca68fbe38b9198dcc</t>
   </si>
   <si>
+    <t>magnet:?xt=urn:btih:9da20cf1a8143f52d041cfb5c5247a820f5e18f8</t>
+  </si>
+  <si>
     <t>magnet:?xt=urn:btih:9ebf6a6a0f48338d9adcc133157ee2b2b929e397</t>
   </si>
   <si>
     <t>magnet:?xt=urn:btih:9eecc4a1ce1f9a40177eeef661448cf96a74c346</t>
   </si>
   <si>
+    <t>magnet:?xt=urn:btih:9f30e99be9912fb4e73a8f1f82d15917658fffc6</t>
+  </si>
+  <si>
     <t>magnet:?xt=urn:btih:9f67e6dde1bc64738930502628df6ef4574e901f</t>
   </si>
   <si>
@@ -176,6 +2057,9 @@
     <t>magnet:?xt=urn:btih:a05c39b95bd608fdef4f2342127052b68d3ad35a</t>
   </si>
   <si>
+    <t>magnet:?xt=urn:btih:a075e2af09da61ef880058a7a3325e17dc6b5d06</t>
+  </si>
+  <si>
     <t>magnet:?xt=urn:btih:a0ad90f4ff9a7128ac301816a59afc7dd675cc92</t>
   </si>
   <si>
@@ -188,955 +2072,934 @@
     <t>magnet:?xt=urn:btih:a29df79f0058f159c46381b77f510ea0f9005d8f</t>
   </si>
   <si>
+    <t>magnet:?xt=urn:btih:a2c4dc948ec346a3bf34be0666f12d07e33e0fe1</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:a3e19d59275c21381245500e0c6402eb9b94e662</t>
+  </si>
+  <si>
     <t>magnet:?xt=urn:btih:a40272431175bc73e91953454642a06321258cc0</t>
   </si>
   <si>
+    <t>magnet:?xt=urn:btih:a488783a9b40ed6a6a7bd02d3759643e5e29dfe0</t>
+  </si>
+  <si>
     <t>magnet:?xt=urn:btih:a58d9d6813e5c158b1b687cc5bd069b90f7b568a</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:4566d46f782bf279acb8b04eccbc6a783bfd6253</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:456f7325ea2d5f470a26c26862adfb15acdb2e14</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4641fd40554b7b69580cd013684ad859ca4e0b11</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:466f0431792e0da5a97343606ead0b9acd8afa01</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4726befc4be4b6061913fea17431ce04e19ba1a2</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:473891f84fcd6bfa8e2c3399713e20715bc6ce24</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:495f45554ea74e8df1a17dbbb263b4e96b8b58ce</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:49fd4aad94400bcd112cf947f91a43802c3db7ed</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4a33a88c5f078b7a997d2b32a260610f285067b0</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4a617e9657c3110887285449f37665627556f540</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4b3e8c3d5e806e3fa8956a13875a9f7d1277107b</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4b81849fe74f329792d1c6baa91b9c6df3592fa1</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4d92d011673ffd1b62974c2e0fc69ef651584155</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4ea299bc745121e8710803cccebcb9a6363f9829</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4eb13bca4ca0db985659a1a1bf785b69e88c0390</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:501448b278545b10c5aeedcc352d3872f24b6d36</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:510c38251b3358151fc4b833ce4477338a0a5ecb</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:443d2498cd6720224920abfb7e71e5a1796a3354</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3257ab5b7c85e50884e6339c61ca1f5a9a266ff2</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3f478b9b5533f4fc0c95edfb3bd56a059505477b</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2b219351999460c2401794e944ac2c2bf526ea9e</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4d59152475ca00baf3d76b2087c9baca7f4b1676</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3bd4048ce69e6190f978507d0731c1d209d39914</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:31dd157cd4de9bc226cbca9c70b5b40fdd4ec4e9</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:506dd018f1ad37d092cabe6d183bd191a7ba104b</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:368ea7b65f89339253da4d7d752316cb68b82769</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4350cff0f29da39ce7025b0c748bede385ab0f2c</t>
+    <t>magnet:?xt=urn:btih:a6e8641e4384693eb085f1d3b27d8e38b2c84ff4</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:a734bf06ff3062788a0bc2d248734c12dbe9e6a0</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:a86b5117aa7389160fae82280af3c455b5a7e280</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:a86e6295b382e0533813f2cf18fa3ad6ce48fd99</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:a8dcbd0483cce17bf5cbf1ad8682be6eb25bdf1a</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:a9bbb122e221d196c9051350f5491a77d3a47f28</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:aa0db6da295956cc43ed34b9d3337542b7b00559</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:aad382ca297320a7a6d7ec35667ce1b67affd9f5</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:aadff914dc0cdf1120e22301e1fb73e0b3f92b51</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:ab00f3b97506c3f20b8810a75a1b642941dbca09</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:ab0be894ae86dc959d79f3f35902d11be7589bb4</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:ab5e1d15a9e8c96a38241af208e888273c2b631e</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:ab890b0ac98097912380a356e0d6c3dda6cbabcf</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:ab9bf48dccb02a525eebf06ade245322d2f729af</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:abac5500db0fe19f2a22e9248f7d295abfdadae0</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:ac8765f3d849013c47e5f5eecc500521abd20949</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:acc3dbf5e1728e6b3c9cabe9bb3eb95c2f6dfbd6</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:ad2705d2f8ff7341dd4856394f3cf581bcacd965</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:ad6bd65fd121d8b008875bb56202e73df69f5aa6</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:ae1ab56368e6fe091a3926f778c915a7566a9ddf</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:ae5ec824f6f70c39c6f382bb39d4938ecdfc8862</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:afc4af08a5547ac761adaccd32c5cb2b5a1f2a80</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:aff7d66de2b821687eb956b82d72c2dc166c5c05</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:b23ef3c079588b65caf7f8cf55bf2cd27eaffb0b</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:b27d8f05b4aaad3bdb352b41d83cb27c13879a87</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:b36c3125bd36c9d24b173b417cff976b5275eda3</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:b3ce44b80041d9934799bcecb62449342f953ef1</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:b45b42848fb60489141864e9f54acc1de069ca39</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:b462ca4bcbcc4cf7a9a25f688f3ca9effb86a400</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:b598bc3b82cb85512cc843223115a7f8010d0b7c</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:b5b2682d974b08ea4030d1df4903729b2e5ddb28</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:b615c3b3cdf61de283882ca825c888c0a92fe970</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:b6afcf716adfdc15a6cf1ebeea2ef72c48c2f679</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:b7b41385015fcc8b5ea21e335a827cc8c74498d5</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:b7efbd26c61bf192d2d9e05206b4825bc04e35bf</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:b8395cd827c0b3f8583289f20bead9001d001f21</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:b853242b87757431d0d00ef7fcab7d961096209e</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:b93bef28dd17181fb086a243de3c9c19c4a42eb9</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:b97b716f3b6315448307b89d5e949f593a26abba</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:baeb333480ba17198693120a88e5302eb30eb83a</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:bb6fa427c68af11e5b13caeb6ab57808e826987c</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:bbd3d9a99996e95306b3f3036479b2d6931347a9</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:bc86ee345e202f63ed4595cbc09efcddc9f4a3d8</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:bca6488b541203fa16b30addcf1b8d0993521831</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:bdb91f5a05375cf8301f030f7975247ee62f0318</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:bde0b9d46ab482f3acd31f1ac0ce85eba900241a</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:be35f6d390f35f1a3e16985fae299b8ba0bbb4a5</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:be538316d9c3bbdbd06f099fea0d2260ddf42fc1</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:becedf62da62099cb94b57b881824ce11c272e4f</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c191e2e8ce35c61de8d1441be54fb61b241d9ee3</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c2bb63120499ab718a5f0458f1f4ffd0e181f9d5</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c2eed8c7265c50c7bc4b3aa745a29f9150a5e3ff</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c336c8d2fcaebe6188c4384342f11376bb532112</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c34efff42f58cc163203cce29b660ac56d6b20cc</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c35bbac1b3e7730322aed351b81ae5a0f5ce4f07</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c36dcacdf854fe04f7fece426fd8fefb97b563f3</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c38aa7324a812814ea9eb6ee5006b92aab1ec113</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c3b79352fcba30dbaecea86b9081e678120806ff</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c3e605652adf5c7643122e7d680ce4cf14bed45e</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c4431842f9224655c1e396ef028f6bb671ae01bc</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c4512ce4a836521819408edc2921edb8bd3d4a0a</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c4658359a039875544056e12df666775ee2b5813</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c47b026d8d26b04d130a226d3fb8ed029fa0274d</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c49659a8fe79e2f434dd14e4ce46a7afb92d9a96</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c49dd478b5a7cafda4a46dbebb9e6d3d5efe1963</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c4b9838c8730631521fd6c33615efaf2a8e586eb</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c4c9390f3ae1bc6052ba09dc825ec049f6bacbfc</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c542961d6cc3c663e755d26a46dcdf640d2ce852</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c555122f2be1791cc45010311e7c36c82f7f9de4</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c566ac1c24e8c2d14e8b77fdb31ee3a667a72a3a</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c5a0eaea24c57edb62a26f955fc854abf829f345</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c62283381109d9222c2e14d7eb1695926804a8de</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c6592872da662e4e72cf6fa9e8914880a18bcdd1</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c690e376b3cf5a6ed406b17e23ddfc3fc15e785c</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c692dc302ab507d246af9f5c2b7152e933e129d3</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c6a00edccad6097670b79c280e170ba7945eb04b</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c6a517bd416192e91a108e8e8b9a06e537712f30</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c6b92f154c218c49f68a55252d653699d416ed74</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c6cfc09f2dc236bb38cd056c587673a5acb1557a</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c6f195c5d6eb0cd2db86cc0648948cb679e90c00</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c703f6aa29d66f72b313cf1d76e2bddd0e7e0cf4</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c70689dc26cee02c31f64d735c825eac0be4b068</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c71682647995cd6285cc8b916c1673da2aa16714</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c759721639d9469b9decf4138ece98a18d4091b2</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c7693f4b7f68c0b34bf21dcbf5af551cd687ed32</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c77cd5645d876a78907073aa07c7ac7d36c470a1</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c7cc5051794a10fbd37e0b5e86dc98450d69d941</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c84daf17da1fd06f7156117bcfa1748ae2df75bd</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c85a7ba2aaf361431cdd5be360b00325c9598a48</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c86603ac141aeb9e9c8f36e157b494f23fe9730c</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c8e796cc30530127dd33e38a8f751d91b9e7046f</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c8fe0cb81031e385c53704e70659e178e5e38bee</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c947187c008e1aa42bce120520d9a73bd901c84f</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c95669964be9a2c97fb7e959f2a7b170e4179da1</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c97552a5a5256248462b72ce9adf41b17709db04</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c98b4c40fb403a582c0a585e647844e8d8d9bf26</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c998e682d1b8c8f4e90d1f02b63585e6c008a793</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c9cba7a3e4bab3cac1d5f569ed48cd9c3ff4ad2a</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c9e52feedcebb1aa344c5f71ca2aedd8ec282b82</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c9f46b2898b71dc57e9e61534760150291e81b40</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:c9ffc9409b11c3a2dbc9f338a6ab8b292fb18db6</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:ca0c7a79f00bd6905a2ecf2026cbc5d36b82dbbe</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:ca557363960d3cec4c33435ce08853b754cc499f</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:ca570d2eb025e6faaf3824f129d3f629eee22632</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:ca6355904f608e13f0184fc09e1f6d5a45a70d75</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:ca793b5b3b4953751f64ee340a9a273c57ed526e</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:cbad778f33fbd984c8ad1d186fc0fa9a8871ef54</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:cc6894478ea362e43c8be1da1d2ae760b7920c7b</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:cc8e9f9c1372e07331dd326a237e29fc703874ef</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:ccd6076bf90f8d7fa3d7a8b71885c6b15dff3438</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:cd3cc030ce6f3e60b86e55c625dc2b257b0d9085</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:cd6124ad8ab92e1107268f3b627297608ae3b0aa</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:cd8908f097a622d13b717fb6e866df4d215f5dce</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:cd8e6d3818f93a4f4186eed0ebb91bf674c7fdc0</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:cdb4bd3b3d970f84133e1a7ee060763c4f40d07b</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:cdd8a740ae681f6ed501d50557d37b2ac31715d6</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:cde15e78299ce03b626bc567d1b13e254afc4433</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:cde436cb7e6b9b6b14446d4386951d184525ae2f</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:ce09fe69dacd3330b8a65b99c5354a809fd8fdd0</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:ce0e699278c819163cf1ddc2a2567b1a6dce0b52</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:ceb37c6b9a24c89a983af0a9310bba5d30ba0f3b</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:ceba2fc064f3cb8b208f45770b55122328c46f7c</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:cecab8405e1d5da61d67836006a6640734987c5f</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:cedcb7e02059b63155588e7729d154f65e8c6280</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:cf0380978110894c6fc24e454cef41297cd21f46</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:cf0c41a2ce8f9e4893fedb74b140711cf7f282aa</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:cf1ba858fc6f8e05b32e4dc6fb3f9d60472b3a3b</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:cf31fcb0c1dd828a389e820866fd29c6bae63f35</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:cf43cb4f4dfcc47bb458d00262634e1fc97719a8</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:cf54437de488cdeb33642177022d544d838281cc</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:cf8c073660f4841273818d8ac9a7b0b7bf83840b</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:cfa6180a2351b4bdcefa31ec2b245858623aa54c</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:cfc25218a006378e790d1b15472e4522a484144a</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:cfc53a9c86988373b4b9947db88e36f3d273afb7</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:cffc99469169b65d81ea805740cb7453013c2853</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:d00d7b83837f2a249cdc2237e900c92a147b79e9</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:d00efff336a3e46e888ac5280556b89b164d4cbf</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:d012903ab2ac41d8832d06da0b8b8ca500d843ea</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:d020d10cd163df96711747d4ca009ba0adcb1aeb</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:d0250a920503216738a62b8e7c068788abbe73ca</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:d0367b241e574b35a485bfb42819e6257fbc9711</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:d07dda854210acbf2014583084355dabad7b037a</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:d0be9cd0f4c68528ff630399f3e5d48c7ea75f14</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:d0c60bf5f8be81447e7f1b3e7b0c3bc4254acd2f</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:d0e1a2a825c39b452702fca2d0e30a5b7bebd0c9</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:d0e7563a7a4264aa0893d518964ae1db5dcd5107</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:d0e9a4adf36af9d0f1232b587204fa688ca92dbd</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:d11242827123687d3ff0577b48014b3d5296a78f</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:d1163156e60c615eadca96dd76d514d3df5eaf77</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:d12e4e3ce00c3a70fb650ac5f4df81b6cff56c8a</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:d13f1183ab44e5c597f69f08634ab51579cc0e08</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:d1486a817cbe96548f9cbbee26eb32d406e9fc69</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:d1765dbd85358d633ec09ee0f1833ec6b33b7376</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:d19792110f25f6a65cf8b9681f27e36e704b95a5</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:d1bd5b02e39081f922a677275d4893fbda5771cb</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:d2df47857d297ab314dc6eb49ccf966fd0798fd2</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:d3778e6dd418c00fd64d7e6937a6611aa609bc47</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:d3b2eb07f9b9fd406b28789a3ef531a2ae9165d8</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:d429e00c85aaaf06e61193d0f98899ce341c58e0</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:d46ef74bf3ba99a75d3a508e4ca06df4fb43b966</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:d5ba24c4aaf49f4c51d01968718a227dad5861aa</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:d5cb2dad1d4558896622a97bf888c69fb18d6453</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:d5d072f62f1f4743a7de984435656fde2d659804</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:d5d979d7603b53d1f94479124dbbc10d1591fef7</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:d63674c5e95cd1a2be2314fd69327290e19c3bb1</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:d6deb36bcaa529ea8c0f27143524bfa88c383cf1</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:d6f33ca5ca9acf64101c2cc7f5b01952e8deb266</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:d70b83ddb61d49e393e63241442a549b45d35ea5</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:d8a7a1f15cd55e33248e7fd71ed5fecc61a21d6a</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:d8f623ea221c331aa08eb09577e57e038a8b8a99</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:d9face3edd769262de29ccdc3e48ac7a25323d8b</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:da405c51b85183f60ba2f1d511bce584c701b675</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:da457d5790a4456acd566e3ac9e95caf26d706b2</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:dc2c7d3bca2b10cb5a5f588307c4d6becc6a6e89</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:dc449c9ebb1ea8a58db58e65f347d9f3ddfb708b</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:dd0a54b3566277fee6c8339c7b59f94eb465ccb8</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:dddbd2f10714c77b59700a5fa1efedf2f1928a47</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:de2c38d7fae83de8ed6a2bceb44c0634fbcf018c</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:de3a7372b00287c1ea51e5109ca022e441fdc38a</t>
   </si>
   <si>
     <t>magnet:?xt=urn:btih:de3b50b79a2f01c11237eeb0797742592f2fbb5e</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:ce09fe69dacd3330b8a65b99c5354a809fd8fdd0</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:310f76f229c75d956b09181dcd849937f4c4e939</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:31c1d3cbc83b7a5c0698db5e7bba4355e17394da</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:321f506f86c09c3ea349742f7e1ef56f04cc4388</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:32a23b9bf884e86969b7cfaaec047f92a7697574</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:33b5b0e8f9d063113ccb4985278da539f413b187</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:348371086208d30b4210e34071fe82d5d4001d1c</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:35308769a7b66e60353f56e55e2ea3bc237a3b50</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:353ef0e48122a952edc7aafda03904f6a4f8ec0f</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:35adff49eb33e0e194c568e3fbf226061fbcd910</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:35b2c217bed242b304f4d29743ea84406f07571f</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3602929ad0ddd9f69a8a79cf7dee77e3f49fe091</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3676bd1eee01c1fb22ff11a7f3484a6cc444f688</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3771568d71997f5eaf2b4e9da0187679e6559b7c</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:37795d8da3e24400b3b76d1219f6d2cfe4f77064</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:37ccd91da5439a5dcd0b3380874ce91e11f676dd</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3812ebee7693c2da4bc582dffc0260d66765378e</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:39b1062efcc089909704f238d7dc4e55fe1b0f4f</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3a9950d18039578aa47a45bce600433cf6bc2460</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3abf5f4b6d0e6836b4b1cca30cc30e22e09a662b</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3bea24fa1131f5cdbd23d13e2004f2ba34da6479</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3c0e4f62e4a8f173a31c219c72911e7cf714a2ae</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3d4a7bc3ecb8fd6f3f4ffec37642ca0ecd49917c</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3f06022952ec30181708086cfc6bee87e3107864</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:40858d86a00a683cf53ba639c9dc9795efed6d9c</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:412e811294c357dc28000ec5cc6ea54d91f8f8df</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:420fd69f848c623d7510cc1bda13439f1c378db5</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4246f9f6ae42d769703d2fa2952c89d61b25547d</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:42aa15864078b8f2d2498e336c935ecc0994d79e</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:44526ec90b6086e1c74fb2a9c435c440adaaa30e</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:44552a61a91a45f174b41d21662ed11001a30caa</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4484c6b21b9f60f489d41cf90ee859e9b54ba63c</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:44a9eaed443d7379bbbc4acdb172795ce9b71cb8</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:44ef3ac03f6662b4f3fa12f6e410fd7756acd3aa</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:45e1c102d18c5167fd745d126e1e43fbbaf50890</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:467bceab5441d7c875c1623a19b942a5194964c5</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:469004e580d626028ac6a2ec9f5321da6bd5c8fc</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:46adc64fd278797edd55a622e3f386ec2b24f35f</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4709b407fb0bcbc9fb07e178b1769db11b127a2d</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:48271ebdbafc3928c537ac9dd57add797c37bd30</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4850cf1467a2755c26ca3a26b69ba5135bd5e7bd</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4a12d6cc2306d7eef6b105826a1a2323b536c1a2</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4a92cd8534b3bd709f815894e035724612edc4ec</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4a99eef0d4c71e97677ea5a27120ac0973394eb0</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4acd5d22b2e6bdb4861cc35d63d9adff79c34b3b</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4ca4525871615da04d73ab2b4191533289831a7c</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4e15266853eb8ce16a4b8116ebe42ab8a1c9b986</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4e5ce3c2797ef4835cdf335e3e7bda962a878e6c</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4e6d3f811fa8080e4aedb645bbaf66de062cac59</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4ee896b13e6c7160c4422564c91533157fc30e2c</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4f7b6791f49e7ac9eaf4584442ad3f4dde8e4a97</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4ff404e1ae80a05dd936bdf61d085275067a0e62</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:a86b5117aa7389160fae82280af3c455b5a7e280</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:a8dcbd0483cce17bf5cbf1ad8682be6eb25bdf1a</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:a9bbb122e221d196c9051350f5491a77d3a47f28</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:aadff914dc0cdf1120e22301e1fb73e0b3f92b51</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:ab0be894ae86dc959d79f3f35902d11be7589bb4</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:ab9bf48dccb02a525eebf06ade245322d2f729af</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:abac5500db0fe19f2a22e9248f7d295abfdadae0</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:ad6bd65fd121d8b008875bb56202e73df69f5aa6</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:ae5ec824f6f70c39c6f382bb39d4938ecdfc8862</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:b23ef3c079588b65caf7f8cf55bf2cd27eaffb0b</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:b598bc3b82cb85512cc843223115a7f8010d0b7c</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:b615c3b3cdf61de283882ca825c888c0a92fe970</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:b7b41385015fcc8b5ea21e335a827cc8c74498d5</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:b97b716f3b6315448307b89d5e949f593a26abba</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:baeb333480ba17198693120a88e5302eb30eb83a</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:bb6fa427c68af11e5b13caeb6ab57808e826987c</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:bc86ee345e202f63ed4595cbc09efcddc9f4a3d8</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:bdb91f5a05375cf8301f030f7975247ee62f0318</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:be35f6d390f35f1a3e16985fae299b8ba0bbb4a5</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:becedf62da62099cb94b57b881824ce11c272e4f</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c191e2e8ce35c61de8d1441be54fb61b241d9ee3</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c2eed8c7265c50c7bc4b3aa745a29f9150a5e3ff</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c35bbac1b3e7730322aed351b81ae5a0f5ce4f07</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c36dcacdf854fe04f7fece426fd8fefb97b563f3</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c38aa7324a812814ea9eb6ee5006b92aab1ec113</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c3b79352fcba30dbaecea86b9081e678120806ff</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c3e605652adf5c7643122e7d680ce4cf14bed45e</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c6592872da662e4e72cf6fa9e8914880a18bcdd1</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c6a517bd416192e91a108e8e8b9a06e537712f30</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c6b92f154c218c49f68a55252d653699d416ed74</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c6f195c5d6eb0cd2db86cc0648948cb679e90c00</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c70689dc26cee02c31f64d735c825eac0be4b068</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c759721639d9469b9decf4138ece98a18d4091b2</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c7693f4b7f68c0b34bf21dcbf5af551cd687ed32</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c77cd5645d876a78907073aa07c7ac7d36c470a1</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c85a7ba2aaf361431cdd5be360b00325c9598a48</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c8fe0cb81031e385c53704e70659e178e5e38bee</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c95669964be9a2c97fb7e959f2a7b170e4179da1</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c97552a5a5256248462b72ce9adf41b17709db04</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c9f46b2898b71dc57e9e61534760150291e81b40</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c9ffc9409b11c3a2dbc9f338a6ab8b292fb18db6</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:ca793b5b3b4953751f64ee340a9a273c57ed526e</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:cbad778f33fbd984c8ad1d186fc0fa9a8871ef54</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:cc6894478ea362e43c8be1da1d2ae760b7920c7b</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:cd3cc030ce6f3e60b86e55c625dc2b257b0d9085</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:cde15e78299ce03b626bc567d1b13e254afc4433</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:cedcb7e02059b63155588e7729d154f65e8c6280</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:cf0380978110894c6fc24e454cef41297cd21f46</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:cf8c073660f4841273818d8ac9a7b0b7bf83840b</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:cfc25218a006378e790d1b15472e4522a484144a</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:519724b4e2fe77195ad4398683dcf71f17d24e1f</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:51f3abf0587c808eeb11f3c0abeb443ca97ad198</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:533ace2bffc61206643bc15ee652895c3987985e</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:536f385c431a59c80d105d6fb8024eaa90069328</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:53a6f3938d84d975bb12e853298c6eaf7662369b</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:53b0531aa9002799bb706f2214b0d20a0d26bdcc</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:54489791bda279421ce164cae3e4ac96a94d3434</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:559a387e201d038204db191460ba5dc4fa84b53e</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:57fe26e62bd5c3195ac587d67c32d86dbf215153</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:582e8683bf1c44cf6b83c3cf8bb38a75b9e29356</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:598bb35fdcfb03e2591a9a4d54b1a74996adf54c</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5a0b02e466008609459b47a86718ae67540ce24d</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:33711be007f79433d40ea5342495b437368b18b0</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:47738032773165d2c4a75a5cc687ee960e83912a</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:313ab87e6322212d316a4e28e5e04f7a38e0fa51</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:8d0fd33ab26eec67772d93efa74a52efcf21dd2c</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:51ed8a7961914ee25880e685a61477ebb57aa456</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:48dc7a4fb3a1a6974214040b4d88e64c9c755450</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:541f54010b91ed27bf8055e52fbf88114951baeb</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2a459151390ca988e7c02a369093bc13c6a05f9d</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:a6e8641e4384693eb085f1d3b27d8e38b2c84ff4</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:023cf41542241510d8eea2845d533eaed36d5eef</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:67cc889e03a55effdee5fe761f979fc6a55e2303</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4a2b4c1bd2ce5f03627440ce32f4878d2ce43169</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:299c74e7a8987b7e5583a6232e9921499f4a4950</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4575df327eabcf3ba5c902d49ea5e5302b327b85</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4d97ff71af720e4fd59b4956d200036f95f57c5a</t>
+    <t>magnet:?xt=urn:btih:decaf5b702f9182eb49c3ceb2a0c861626dbf6a9</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:dfd5d872748b656baf7625ffb550eb51c4d60343</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:dfed558df5dff09a981c2a43b0b0a815b29815a6</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:e01ca77daeb3e66422f62c65edccdd26d3ca3e4c</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:e03ea25d95b9fa0b79e2721c4398abb8c9715467</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:e04af24fa4840e3a0d08427b524ce767ea0d43a8</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:e0cf339a095075498b3faa6e4cc2b642456e566f</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:e101ca986c95128ba2919a5d6b24b56ba79a9a00</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:e26960d8c581fe16ff81ce55d94228d3f889983b</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:e2e40cdf59f2a8c71200b0d41385215cfd73c611</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:e3dddbcaf3c6de0f7949f01d025520b61f2d7641</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:e3eaa88df04a8efb9ac097a72575cb320de6b3bb</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:e455340ee6f4f28e737b96345d9f3f852ed2a07b</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:e4efea325a418c8bab5831c3ebc12eb58a0476fc</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:e557c56af74d9f5e028d0e8dd5cc08147cfe7a4c</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:e5c5f263efa4bec7eb57ae1472e6311c203aaec9</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:e60e3180d261a1e9d4c8af3585fc974c22a55c49</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:e7ed5c5519419273a90c607952f305a63624af80</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:e8c92644623df31f1242e91d3911d1abb4612994</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:e8cf891f886f895d52317b06a05449bad1c02761</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:e8f4ad7791f9e9331508ccd9acd2d1e10fe1009c</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:e9481fbd5d45cd7a9681a23b29e55b3a166acf38</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:e94f1f54515c283fccde63dc0afa9b296d62c6f4</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:e96a12da61e774a1ce1fd13090be4c5ab45c8c33</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:e98c4d5cb0c2534b8540cad529626965904f2457</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:e98eef21c25f63bcc6c38e2741032c4d64de7d6c</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:e995fd680274a6852dc5b211167486ddfb68e346</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:e9d92dac28d340b375d9d3597c873f02bfc2ecca</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:ea4154e455a872fdbabf60942baedefd0f0dd42d</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:ea75d157a54be66c3b0af475b37f4b7313d16031</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:ea79df10d05ac094921a420e38923921040fa19a</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:eb33fedf2e25eca8136f46b505752df2453f9a6f</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:eba15d481c14b67da1a7bcd4730aa540fd8e9ba4</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:ec1782687a25ba5e2d9d2180be4409b1b04601f7</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:ed66644e79d3d37166af5b559cac73d0aaaa525f</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:eda7c5dd0537c2f6afd3c2614057145cc457deec</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:eee329d328833a69c953216de3e974ca4850dee7</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:eefeac0ddb1346e2968f70ca082cb8c7a73695a1</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:ef8e9d6f8512f5c3f1c8ed3db0c8dea8e056a749</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:efc27c7ffd7e8de5272203e835c4dc3cc064156c</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:f142b775a47f3439c39d8dd521a00f8b744b4bc1</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:f2245e6ce68e30ef2bb5750c1d22dc681b42b497</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:f230fef05b8c830b3680a4a1d0e88244f78cd8d6</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:f3bd1b7eb5b6ec2d6a0c4b7ed9b659cd403ff0cf</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:f3e6ef0aa47a39f871d9777546a1a5878fc0a893</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:f41a123707579853eedff2a6ec6b1e1c2a6188f2</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:f43b4444b4e4601548de84d3123f160b51f934c1</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:f46e14f3bb142169f8b79a465485a1de28699447</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:f4abbf74ca074f7bb9f77669c6937d2e91c01414</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:f4b482378f65e41de27d1a78f7ea19a26d8877ac</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:f4c238b0f69c1d6ceefc556c8432d1e27938712d</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:f4e3c85f6a542be3ee4dffccdaf6e17749177996</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:f4f8b5e88d07f3c20ee67a9dbdc81328d72d38a9</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:f52b2ffbd2ef478fe56b55bf3acdb8948485a8ed</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:f5a76014ba9fa5eee52c7bb624d9d7b879a1666a</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:f5c7f31aa780c341f69351a3a6e2b1c381c74de3</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:f5cd2e81ce640278a7c02f661075bf868f93f5d5</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:f6090910560340032a77698dd74a2a9d0d904d25</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:f61d60e34313947b9060c26bfd1b72719806a734</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:f627b9acaef9c13eb0e4e902aaf746e73897c682</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:f63f12f51a99471b7a53084ef328ebcaca511372</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:f654751c63a11076f500d37142c3c32a27ac3006</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:f65e0e823686983721c45fbd54ee9fe096d6ed05</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:f65fc37d3328a273d4ad491cf491c57599f170c7</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:f6774f9c2d58089cc8add3eb2bf0d4ef9bf1a4a8</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:f6afdf5711a0c3535469d9eb1a26228c83f2b2ba</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:f6e585331210a6c7ca4c6104779e5f111804087d</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:f6ee436d3c28697294e1637c72b2ea63e5ab8dc3</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:f6f35075f7d2d6085c00275fed354d184e0455c0</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:f6f6cee0c89492acd9ce1b10107b54d53ed2f98b</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:f73f3045b59b32fdb5905a7233619c6fd9617cd3</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:f73f576de5a5b8863b14dc77ff1b34a72c05ea3d</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:f7847fe7611cb7dd0320d620eb819f595861ba31</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:f7d599413c058bdf774ad70894ebf64aa2b29017</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:f7fd72111a57bab31dbdc603d1ea0ad70d02426e</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:f80a3dcabd716307d146a196888ccb10fd813841</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:f83df5a306961fcd42cd18116b866230b23aeb63</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:f8658f6be7e03d1c2fb128fb8affd181d8d618c8</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:f8bc59e616ec857d9c1e33261287fba132299bc4</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:f94ae24507c9e510066b104809d681834cf03368</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:f96733e907ef33eaa4cef47ac4a59e94c5d3c345</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:f9935dab79ce2e0ea186db9e4cc742670020d497</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:f9b71bdfa3ce1a085daf9f6a5696dca2ff0f801e</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:f9f6fb9d1ced8e7217c5d9cbc9feaea13f38e1ee</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:f9fb8651c3561d6291ce99777a806a0caccfa8ad</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:fa0ad126a44d22e99a6dbdf1d70d016bdac79975</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:fa22d320c08c1f14ad5741062f6b16224febfdcf</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:fa2d7071cae55142eef04c5fd7dd458a19a18ede</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:fa38383a1ce94cac44e0e13bc61624532f0e091e</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:fa60f149d9fba86ee9a9d109393d1e1bfc37dbfd</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:fa6970ebd0900094f9e140439b8bd2169646c939</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:fac8b8dec44c7702d31293aa333806d0745113e2</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:fb014b46c8cf68a109c277f2c114e3e8de0df420</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:fb3252c1f434c6b35398f9ce154ea45f46b6b142</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:fb47e5d4e5ebbd0a42610aef5b5176551dac5324</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:fb842532969d05390152274858ca447dff7fe9f2</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:fb941dde99943c273f6909bf70b8f8b497e7e793</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:fbd9a60be90d891aa09e1af3b2b1bf0b293e67dc</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:fbe5ea567a8cf7ec8021c3e6b77bccfcfad2240e</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:fc2cebc430eea65d487499c672f878cf8303a385</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:fc68367ab28a5eb10871c7f2a3ae59d1ec2f3f7f</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:fc6d1bb89f141364d92a51e558ae2f46e57911b5</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:fc6fe59281ef209a13166e6ce430127c3fcb00e8</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:fc7395f606ef51484eea31b61e869ded4c4af937</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:fcb406e769f52e680de44ff1e6eae5510160e722</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:fcc3f0cdf4edfcf71b585053583f4ed134da1614</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:fcdb1d2a30d373a71392382bac2a92ff22590c84</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:fcdb1f54f362fa20850b43afbea8dbec33325b89</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:fcf022ac8ad6031910e1991935af155c7e12fdb7</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:fd04b726dc730e813734a5d40f565d7033ce6ffb</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:fd84ff8e09eb50ba35cf3e67ad0e2960bba7aece</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:fd9b93e87f06503b53899fbcb79c2c3cc464439b</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:fdaaa6d298ac1d2be87ab54291d1da5ec3237a1d</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:fdc32f74c3cdeb01504aaa8231f66a374bd6c743</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:fddd49269ba252f910f2ce15475e11040d1c4c42</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:fdfa5f6289cba3e47d60558037ceed6a72afe307</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:fdfb60287ec964c4c3adff0871e4110c46ec4b22</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:fdffe5d7126d72e29a3141d7276672bd4aab7bd3</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:fe0a4fd01505dd9089abea0baa544f1bf9c5dbf5</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:fe32e86253b039af17ef38705b4ba28d69eeb7aa</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:fea6045a60d035f9afafec091966c973fe3c96ab</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:ff0583a60aac3fe05004e91d75e8ed3e0ca2e3ec</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:ff1fb71d62ee067a329c488db0593b6de7e37062</t>
   </si>
   <si>
     <t>magnet:?xt=urn:btih:ff6bd7ce3704ab49bdec07759f381ef1f8b851ac</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:dd66548b8478399b8a576e1fda9f478d526171cd</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f2f90e6dc7810265df87c06ba0ec1b5c84737ea8</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:505e91f0d3c95b850f4096932e6d3d80a7ae5422</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:509bd98eac24a3fae51278b49e06c16f84505875</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:51b5315f78f0d3203894cca9cb034c5ec9828dc8</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:526f15f0902e746514c7da8b1eee56e9f583ccc7</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5283137c9d4c4ba32aba7d87a6bc2f531308fe64</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:52b3a34b6be32f3d7209fc8c2678e905825a53f1</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:533713de520ba43ec6191b15a1c52269f14906fe</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5394a82a3347d3ce7f502917e01997ad98f92d38</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:54222e70e9f7f1cc6c42b128d05de1e6be3c45df</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:548e64bd421864cb0e85c5e8c81077d16b41646a</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:54b764262e5d7f0bb73d07de63fafdd889c92efb</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:54d3d8fee9ceae883a1913f5290a28dd4e4375af</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5500f0a3ba61011abd584c8df66cf13888ddb0bf</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5636b0cd30b5a6a611bfa4aa209bbd19e7b3d5bd</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:568f66a4afda15bf1f08d000c47feb567555c9c4</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:56dece437eac567fe000d8c8b45b35f52816891f</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5886cdb9b61040c01617b9790bc40d19f34b679d</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:58abd8287f897ee8c152b4deb518ff78a3b80fea</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:592bac122164bcd114b890c4b03332a6b17f6e8f</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:596e55c581f7f715a38c9164c55338b30ae17802</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5970c1e78be1e5b7e888860633997938b949c447</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:59793c851b94cb6371a09b7d6f0aa1c9e57ff74f</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5990a591330a7f4ec30a61d405e641241802b940</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:59e0d9342ed7c5898cbce7d3932837332548c635</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:59e4537733fd09189d90edace74102204ffd356b</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5a54a2ac47bbfa6490d5c2dfd6eea74ab45a81c1</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5b20255c5ea588afc7262246081d53d1d3151bec</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5b30d4ed752c0c4d2b221858b72bfd9e9f643701</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5c67cd8001a0fa53e91d6802b43a71a229559d39</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5cb74030eb130c302efd8780a3f852e301397a25</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5d0258f18787d49971136dfbf87e2d500f910a20</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5e32729600b04de8e729739641c19577b353be16</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5ff9d1b438e4cfe60ffea7e95736d0dc2f3cd006</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:61371e1354febbe07a14128332c593764d637fae</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:62a9f6bd188deb6943a661e864c9b94a7fbd77a7</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:64b250dce83b4134c62cf37c1034a633c79423b2</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:669e67dfa1ad6e73ff83c27ff9dc87258e72fb8a</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:678ab547730d7e179d02871ef7a05aa2bd9547a7</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:67bc320d632d3b0df83e308f9f3f6725aa6d9306</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:6ebc7a8cfaf62d764918dafa5a4f065265c1a02a</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:722a72422ac35dcbd216afb8c632fc131d996cfa</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:7299f613dc5a9082d56ed8489aed0700f8806253</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:729f92a17dd2644633f475a09997c0afaa661207</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5ceb81641b862d0801e821b5611e9044608830b7</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c86603ac141aeb9e9c8f36e157b494f23fe9730c</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0492fc84509b8be145dda46a6654a9b208bba2de</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:47cf435a57043b9e064c0d0be2429912e56ed4e0</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:46779a38ab50f204319b773c403fdad886332e2f</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:6abed1e8a7a058a2fc8071a9bbbada40b065791e</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:874869e2959732c58b27bcedbcc1933390ec6f4a</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:d012903ab2ac41d8832d06da0b8b8ca500d843ea</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:d0e1a2a825c39b452702fca2d0e30a5b7bebd0c9</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:d0e7563a7a4264aa0893d518964ae1db5dcd5107</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:d11242827123687d3ff0577b48014b3d5296a78f</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:d1486a817cbe96548f9cbbee26eb32d406e9fc69</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:d429e00c85aaaf06e61193d0f98899ce341c58e0</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:d5d979d7603b53d1f94479124dbbc10d1591fef7</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:d63674c5e95cd1a2be2314fd69327290e19c3bb1</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:d70b83ddb61d49e393e63241442a549b45d35ea5</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:d8a7a1f15cd55e33248e7fd71ed5fecc61a21d6a</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:d8f623ea221c331aa08eb09577e57e038a8b8a99</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:d9face3edd769262de29ccdc3e48ac7a25323d8b</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:dc449c9ebb1ea8a58db58e65f347d9f3ddfb708b</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:dd0a54b3566277fee6c8339c7b59f94eb465ccb8</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:dddbd2f10714c77b59700a5fa1efedf2f1928a47</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:dfed558df5dff09a981c2a43b0b0a815b29815a6</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:e101ca986c95128ba2919a5d6b24b56ba79a9a00</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:e26960d8c581fe16ff81ce55d94228d3f889983b</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:e3dddbcaf3c6de0f7949f01d025520b61f2d7641</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:e4efea325a418c8bab5831c3ebc12eb58a0476fc</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:e557c56af74d9f5e028d0e8dd5cc08147cfe7a4c</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:e60e3180d261a1e9d4c8af3585fc974c22a55c49</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:e96a12da61e774a1ce1fd13090be4c5ab45c8c33</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:e995fd680274a6852dc5b211167486ddfb68e346</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:ea75d157a54be66c3b0af475b37f4b7313d16031</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:ea79df10d05ac094921a420e38923921040fa19a</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:eb33fedf2e25eca8136f46b505752df2453f9a6f</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:eba15d481c14b67da1a7bcd4730aa540fd8e9ba4</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:ed66644e79d3d37166af5b559cac73d0aaaa525f</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:eda7c5dd0537c2f6afd3c2614057145cc457deec</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:eee329d328833a69c953216de3e974ca4850dee7</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:ef8e9d6f8512f5c3f1c8ed3db0c8dea8e056a749</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f142b775a47f3439c39d8dd521a00f8b744b4bc1</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f230fef05b8c830b3680a4a1d0e88244f78cd8d6</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f3e6ef0aa47a39f871d9777546a1a5878fc0a893</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f627b9acaef9c13eb0e4e902aaf746e73897c682</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f6afdf5711a0c3535469d9eb1a26228c83f2b2ba</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f6f35075f7d2d6085c00275fed354d184e0455c0</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f6f6cee0c89492acd9ce1b10107b54d53ed2f98b</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f7847fe7611cb7dd0320d620eb819f595861ba31</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f83df5a306961fcd42cd18116b866230b23aeb63</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f94ae24507c9e510066b104809d681834cf03368</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f9b71bdfa3ce1a085daf9f6a5696dca2ff0f801e</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:fa60f149d9fba86ee9a9d109393d1e1bfc37dbfd</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:fa6970ebd0900094f9e140439b8bd2169646c939</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:fac8b8dec44c7702d31293aa333806d0745113e2</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:fb3252c1f434c6b35398f9ce154ea45f46b6b142</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:fbd9a60be90d891aa09e1af3b2b1bf0b293e67dc</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:fc6d1bb89f141364d92a51e558ae2f46e57911b5</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:fc7395f606ef51484eea31b61e869ded4c4af937</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5aca700c2b451fbb9472864f52aa79f3fa191aab</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5ad5435732ecacddb163944bdb29bc8793e9cb04</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5c13a906131ee9a01ff0eb209a5e58f78bd05fa9</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5c79e96c1c3c59553f1693118db44bc063d750a4</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5c7a8ebae1dd2a8ee53bbbd24da7889d98eed00a</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5d86c7f4f3228c1b6c8cc60afde8e58e13792c86</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:61d4197b65439a91675cee6190ef1569e976a954</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:6264ed7eb7b3138137e1af85dc2d3a6429eab672</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:62e96a41018ecc2379f3fdd5a1417a0078040e01</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:7e305dbace575bc641f906a84fbf9b563608e411</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4819c04224b1bb704e2a42402cf98b88c4316d21</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5e10c9c3414e6abee3f8505ba017c1a69aa12bb0</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:94c1560a737dd495b2bd1af4d417193ebef57212</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:64cecda8a31ae5e8a625b47ff04f3fb387109756</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:37a9b30dd21bc1ec6558fb62d0b6b1e2ebfc53aa</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3837597298a2036d724c86e6e268b3149b4ffdc3</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2766ed82e5637b4f4b958d05de4e48453e72d7a8</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:48a1ff5c72cd6d24990e624e424bffa5dac9a39b</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:74551308f72025fdbef6be96b623b4a3163de13e</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:084e7decf5220931613b8cf0d1f61815fd3f5e2a</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:03be7c96fd3b558759b674f75e802240d940dba2</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0fb41bb563de5933fefa8e7adaad54d3e9bb483f</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0704232f88478cd9968247049086aab94c9d31b6</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:785c761a3aebab3311728c9d588cc4b6801c4a24</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:599a4b2475966c592f823fc2e07ee1a1272f6c2b</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:e5c5f263efa4bec7eb57ae1472e6311c203aaec9</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:90fbe96322368351d8d6e6708a8fbdebc867fa93</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:007ea690cd76442339e6c3ee866599b70ed74afa</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:132d5ba95916efe0947afa145e9706654c17eafc</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:272e5aface0a3c61607e1b2fc9d81f59499cdc89</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:27a4a42eb36d183e5ebee5ee73a37796775bc5b8</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:cd8908f097a622d13b717fb6e866df4d215f5dce</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3615fdf64ecc1b834cf312b4d5d4ccc90f2f0004</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:28ecb19efaee90504f3540dd6ba6958a43a1a9fe</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c6cfc09f2dc236bb38cd056c587673a5acb1557a</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:380e301f739101860585f57511c9ce6e234ba7d6</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:e8f4ad7791f9e9331508ccd9acd2d1e10fe1009c</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:895c7a2ae27a0c45de1ae7c425231d0eddc55d70</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:cf31fcb0c1dd828a389e820866fd29c6bae63f35</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f65fc37d3328a273d4ad491cf491c57599f170c7</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c4431842f9224655c1e396ef028f6bb671ae01bc</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:7725dfba00e1d2555d71d6f5a76179a5bf678848</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:bde0b9d46ab482f3acd31f1ac0ce85eba900241a</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:d5d072f62f1f4743a7de984435656fde2d659804</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:d2df47857d297ab314dc6eb49ccf966fd0798fd2</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:aad382ca297320a7a6d7ec35667ce1b67affd9f5</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:8571ed1d595069b7c8679cd4171124d8b98ddf26</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f8bc59e616ec857d9c1e33261287fba132299bc4</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:001a372783d66a24276bef2f8928549c88d4c635</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:fcdb1f54f362fa20850b43afbea8dbec33325b89</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:fcf022ac8ad6031910e1991935af155c7e12fdb7</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:fdaaa6d298ac1d2be87ab54291d1da5ec3237a1d</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:fdfa5f6289cba3e47d60558037ceed6a72afe307</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:fdffe5d7126d72e29a3141d7276672bd4aab7bd3</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:ff0583a60aac3fe05004e91d75e8ed3e0ca2e3ec</t>
+    <t>magnet:?xt=urn:btih:ff7687399bc5f83ba185bbcfcabb04ef38e99b6b</t>
   </si>
   <si>
     <t>magnet:?xt=urn:btih:ff7ac0167b0828d392b377781e8722a671f1b677</t>
@@ -1145,2059 +3008,13 @@
     <t>magnet:?xt=urn:btih:ff85492d4601df1306ef925c996a461bcf581f0c</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:57792aca07eee28bbc2ea66f07235d85e4219317</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:02f3e2322222f927dd582d122128514347478e23</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:79b8fa0bc9b6e04d9c8ac0d95e5c3fb362d9cec7</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0a81538e1d5092fc84057d737ff31633c0b1857b</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:fb842532969d05390152274858ca447dff7fe9f2</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c692dc302ab507d246af9f5c2b7152e933e129d3</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5aa779d8cf42d8216a2a0919ded426833956d2b6</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4b76e99ccc575c0abea96bbf8c024ac97900b5f3</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:327cac9ce19c0f1d83f2dc46adddcdb9b72c75b3</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:e3eaa88df04a8efb9ac097a72575cb320de6b3bb</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4486bb109cf2e1975a060ad92110fbe356e900eb</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:28fa2cc903c04d2b2cedb1ae2b54fb27bec9b75e</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:6901b51822193eabef55e2911522eb1751652dc5</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0ebc9b974efb974437d87fa3877d20d44ad67b3a</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:e7ed5c5519419273a90c607952f305a63624af80</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:64e1e31a32f634363265f4d3842a8c2828b12371</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:653659a8a999d8b91233d24b4a8cee7326f67154</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:65a78654c73d43023bb23e06f6ce9df9bf4e7bd7</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:6af90699d0659c3e71755d1a54b140d030db9af1</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:6b4f8cd210f474a80187df8105ee136ee1e6bc86</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:6b8eb3db398e37682133facbebefee232f617176</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2b9ae86e3b019711ae7d3f1908676b8d2e2743f0</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:d4e4b2960f9c83b13bd294f5fd4004d48b10d923</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3e42fa55d91dd447749cb98280deb965cef20667</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:841d9b79c9750da6a2e99c8780203feb553ef7c4</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:ae039980b801fe58f4cb028435d205282a52a5de</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c336c8d2fcaebe6188c4384342f11376bb532112</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:741f62ed726942bb1b908924157b5ce8cf8dc0c6</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:fc6fe59281ef209a13166e6ce430127c3fcb00e8</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5c36d8dbd682d270859dd5015585a89361b60470</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:d5ba24c4aaf49f4c51d01968718a227dad5861aa</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f3bd1b7eb5b6ec2d6a0c4b7ed9b659cd403ff0cf</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:eefeac0ddb1346e2968f70ca082cb8c7a73695a1</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2c40b68dbb4aaa314e639ece76e747a01d92963f</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:fe0a4fd01505dd9089abea0baa544f1bf9c5dbf5</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:50e45d785e9e7c6308a5d263df160db8d3ffd9a2</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:b5b2682d974b08ea4030d1df4903729b2e5ddb28</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5087f57f3d7239dec57d8b12ed384205cf586b37</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:744527bb200c04bb60f877fd4eb894f06b89e309</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0083ac9fed705e761b4565e88136c84c4d4534f9</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:00b19eb195da543d79bfe7aecf2fdd35919cf09b</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:014081a32c57f72aec36ab8acdab711702251a0b</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:01fc0800b3cd20ce597eb71894a52a9705351ebc</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:03168be24ab5bd28229d926a2b5f70ebc578afec</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:033e00742f7ddeb5d85bed53e656e3184cf3227e</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0406a5b58ce363698b934efddaf858f093def615</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:042825b6ebac84b2d491a201af2e41154a7fab74</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:048866cbe02b8bfcb8a1379a1a7716a4d046f603</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:04eb3f0e993c8e18e3978c9d20b5e3ae017e667e</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:04fe15b15e7217b85c17a34b8393904e8710231e</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:05959cfd355f10c64058aa25cdc3173def7971d8</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:07804285b615e4faf996d9403750720c43c2b01a</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0969e1a00e816e926f987ecb99b38f059657b1ad</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0a4c3b01c3c66389db0b7884d41e4d1abb650f33</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0ba38eff1c1810dafe45f943d0c0d5101551f1ad</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0bbc16b1562839e2c9d8000008998ac6949a6f23</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0c302b0b807157791dd36f79056056c22253dbc4</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0d28755d531ac86555bf9da348ddd8a7280199f2</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0f01025198558896a285621a9d8253cd02c4a4e5</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0f5963b9cb8fe8f2e319aaef45ad9d020544f1dc</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0f9bc39d02d2c9befe574f41bd0805c615ee7617</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0fa10cfebaea28eca45f42388a2d9d15bf0b73e8</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:101c27c141c647c399606ba74d8d5a87fffae99d</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:104da3463e9478dae399cdae8e52eed459648f82</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:10db758f8221e731365c63d9c05007af3efdd33a</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:16111b959898153cef3ea61a2cddf12ab2b8bade</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:16c8a0777873100e6e8450975f32996b4cf08f54</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:195b2307e8188199c4fe1d81c595cc519de7535c</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:478b889f63a8868f173d8f5663baa0b84d07914f</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:07bb7a585abfc78137900f72f163bd39284c7606</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:ad81ee87e3488d2bb272f1a077543a240b7066a4</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:07f553f8442200f4e4a19675bfc3698bb52f1cef</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2a2d3c09113e66f6f4e17b1c206e0c2859ae03db</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4468c84181640b6aa8157ec79001f1e95973fcec</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:738a229c755e8ec0f528cbdd3c1b7dc81086b4e3</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:73ff4cbcb967d26effb7414e1a09a40a9fb1fd42</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:57a582305734b95be93976465bf1ea3b849d6d75</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:837529609ce1d9eb5a58e5627ea3a2dcadb5247c</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:373217b785617982237ad84743287e94574f6709</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5c0735c692fde1e42b7c40b187328d11e57a42b3</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:fe32e86253b039af17ef38705b4ba28d69eeb7aa</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:e01ca77daeb3e66422f62c65edccdd26d3ca3e4c</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3057788fdd39eb14fbf581ef59442644b9f38361</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:01dd62bff1a692019ff6e7f1bf9b7f908bdd0216</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:020389cbf75cf8e1e0ffcb4a692b2418c12ee45b</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:50d1b19753574c6a42522f56546a7dab9cd4be85</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:385edf16fb91f53f82cfbeea88343b509357e7a3</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:1b52970aa5bc36d748cb41407c2bc192711df581</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:1c5e840015279932e73d6bddb2b0c1aeddb2b3e4</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:1c88f8b262b2b9ed3fad708d3def1ae838495b64</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:265e4b2470723996a968732f00e29dbe491bbf9f</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:26b5e80399b75ce81a674b7ccffd1ae31ce694f4</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:27e94881181fc05525aa567a606eee18835bbb83</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:281cb88ea3c4cfceb14fa5d1d55aca2189c7465a</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5a4dc3400bba3a871831c8ae80acf2bc60a0343a</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:fddd49269ba252f910f2ce15475e11040d1c4c42</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:472b41b872a65685b315af9a2aa34bc4ba244880</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:457da8744c5ed035a423fdf4d333e4b7caca70ef</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:52f9576ca3440e101e498be4f768197cf9a96dbf</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:d19792110f25f6a65cf8b9681f27e36e704b95a5</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:299ae62afd80809d6addcda1a1e8ab58391f430f</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:52e9250e4f628c1b74b56505c2f1cf1c467e5f83</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:cf0c41a2ce8f9e4893fedb74b140711cf7f282aa</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:78f983a60bc0dd899151a94fa38cf50e3887168d</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:7a945bda5595f8a98a9f5da688ba9cc2abe2fcb6</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:7be9e1c0e6574a1890985d14a42cf6e33072e1e6</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:7d62658354b2fdb4063db68a801f4793d4acd858</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:34c4cd26b90d83203e3874da143febdfde031761</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:513ae9870788e5b490869dc910e9622b6628318d</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:7166e63cad0d3922225cbd97f5d5e4ad0f3097a1</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f2245e6ce68e30ef2bb5750c1d22dc681b42b497</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:32dea6679edaa76655222ba335305566fe196fe4</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0d92c97b30845e8c9a3c0e575608ec610419195a</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f2f556424009ff04cf87593ebe049b71b84d4b35</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2b0f1f4e2b1ff25cd60515fe55b690ee9dfbef83</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5492ab8c0e9debcb5a9f06302f9b7d66579f3173</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f4c238b0f69c1d6ceefc556c8432d1e27938712d</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:469892c579d806dd122dd327bc7c0f2f4a2ad76e</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:40c92d9769624fa43bf759e5c58d5732dc748e1e</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:cecab8405e1d5da61d67836006a6640734987c5f</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:1119069909e0d8231e22f3d4b882dc1996d1ea83</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2d26585fc592d87b7c74e0d9d4e591853bbb21db</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:7065d3b859351d62e3c35e0f93bbfaf23fb516ec</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:510ee7b19d52689d3d972251834d406d26afc14d</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:56d527c652d2b1535408f3073cb3438b14425981</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:57f4df3bee06f1eb41ae6cd0e202505a09abd25e</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:28f513228547a557fb25912dbf6ae2eaca553a0a</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:7fbb76ede97b5c1ff261e4b4ff201f7409d1888e</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:82bc2667ded162bd2c04b26935d46ffa5f54c4f0</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:86961ba39226da222965e637077458419966479a</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:885c78862362422f532255dd8eafba47f46adcc7</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c566ac1c24e8c2d14e8b77fdb31ee3a667a72a3a</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:b0c0968ab36158cfa6f4c3939292bfa056658705</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:ccf51fd483236dcfb9a8f23c988bd3d634dbb4e5</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5b10d3f94ebc084e4aa46c0446b03099017b7e19</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:a8ea3e0815eb0ba4418c7aff481de3d134727d04</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:1cc55b650ec572f23e80154de901c53efcee31e0</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2f66730e379d4003e4fb3a496bf4b148f3e80300</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5a8495e0fcf4d25fbce3e9651f7933c535332538</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:fa0ad126a44d22e99a6dbdf1d70d016bdac79975</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:33647a762a0f79a72e949c3b1d91410898c35060</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4cc0be19724aa83e8061a376ef0aa6a379ac80f5</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4f099789dc342133a6a30bf4cb949b9df7680de2</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:d1765dbd85358d633ec09ee0f1833ec6b33b7376</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5ee97b3b01910d2cedb3fd2f16139efb5b771ffa</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:cf1ba858fc6f8e05b32e4dc6fb3f9d60472b3a3b</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f9fb8651c3561d6291ce99777a806a0caccfa8ad</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:447c58142a8f62bea4d16d2d1ccd4af944675599</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:59f1c2add4a011054b3138cb7e3394f0d06afc79</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:59de0f98cf65ef7e9577062f62859351ce210b2b</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:aa0db6da295956cc43ed34b9d3337542b7b00559</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:430892547f924c9a1241c264c452a75fa1a72466</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0b37810ec866e899d15818ac4f68a2880135cd9c</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:8cac5dc61d12d7dfd1b5329489d3597fb938459f</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:8d95bfeb6d4e5f232f202bdfab8f06ec11209c26</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:8dddf6722e920ef47d96ac0756a3872fa9ac8d9b</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:945be7b6b063c65bc7ff0825d9f62d34b9a2c58b</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5a4a52a282ca3a70e2364c7c42d1c23d488b94c5</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4f987fbf332662b34159876d6fdf665d54b6e93a</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c5a0eaea24c57edb62a26f955fc854abf829f345</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:09ee8185e3c664c7a6d30d1a83c0067317353b28</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:35866198fdd17999eff9382e21d0bdcbb5ee0361</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:b0dac0e38f624c4e03cd7e022a55ab9e407123ef</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:430265cb535d50f77fbeb943cbbbada475c80c06</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:53578b888001271bd428433afb5ab0f923c8aa12</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2b025eb859bf2da3c8b992147e261e3384768d83</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:8b2882958240b43f5a67bfc90f8cf65f090fac09</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3772231f02eb0a3fa4369add00efd61418e7657f</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:e94f1f54515c283fccde63dc0afa9b296d62c6f4</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4d69dd586d8ee7f8d0248fe19bf24579bb299eaf</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3a7c53a10d1b3cb756b4c04a27cbdc381f113dd6</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:57bbeaf3942118aaff8b7228b3ee63387f460318</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c4658359a039875544056e12df666775ee2b5813</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:45b2720a76b148af0c2e2844ca611f7cca7d17fa</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0c7b9d68a1e9fc4a2f67dbd214dc42ba8fec4997</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:cc8e9f9c1372e07331dd326a237e29fc703874ef</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c6a00edccad6097670b79c280e170ba7945eb04b</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4b241fed126308bbcb8be32a98ada04988bf7338</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c34efff42f58cc163203cce29b660ac56d6b20cc</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:99a9100f4bef6c87ae843ebd77a511da9d1469ec</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:9aa82cdd8884999817776a4ad7f69d40fd3b7411</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:9c99f25381a03bf2c5c04bb3f1ff8e5b774c4d95</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:9da20cf1a8143f52d041cfb5c5247a820f5e18f8</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:a075e2af09da61ef880058a7a3325e17dc6b5d06</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:a2c4dc948ec346a3bf34be0666f12d07e33e0fe1</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:eef1fa536b7799d9236de9817011a19c4f5dccfc</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:d8f16ac9e3e117a4b286f22229122afa8da7408e</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:6b86e7b9877b11695ab0b1bb5b4a7c7b2a14b833</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f654751c63a11076f500d37142c3c32a27ac3006</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:9029c9ebf8c3c71ab5709c5c1296cd81dbd1143c</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:d00efff336a3e46e888ac5280556b89b164d4cbf</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:fea6045a60d035f9afafec091966c973fe3c96ab</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c4c9390f3ae1bc6052ba09dc825ec049f6bacbfc</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3c1260f309ba1d7bda277e6ac9f41d268edcd361</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5517640c56d6e8d8ba65550e7af417793005d168</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:546964dc024fe412672b54e11bea086033a97bfc</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c7cc5051794a10fbd37e0b5e86dc98450d69d941</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3afca03fad4d8db8fc48f92e5a902ddd3bf48bc6</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:de3a7372b00287c1ea51e5109ca022e441fdc38a</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:00b71b72b51f96e16c1d8d07e34a56ff42b583ba</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3bf1a428822de7e12ca5e9e4426cbabed12fa53f</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:ffce815471788dbfc4269333e59623e5ef74183a</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:38d6d35670af52d151bb894e88dd0cf0e8b95fe5</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0223578ff29c348eff9fd5224f6b5480a6f7e3ce</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:281713ecfe14a72cf8170a587a887a0d45774324</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:1c2cefaf92c8bbbf581be8466edb5a6725d2ff3a</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0e68df905934d4c3617dfacbfa38e228bcaa3f00</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:d0250a920503216738a62b8e7c068788abbe73ca</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:585c46051e7c529ecf76dceee7524fb0bf46e56e</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3ba5657dbe63888304392925c568421bfdf39f2d</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:648cd6a534e4d294751d1b92b549112011327184</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:fcc3f0cdf4edfcf71b585053583f4ed134da1614</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:488d5d23f0316189c75903ef8b28bca7ade319d9</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5f1524b00ce1659cab1c53c011575a461a68a20c</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:27ab11ab48752011da373b4d027f4270e70ca001</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f6ee436d3c28697294e1637c72b2ea63e5ab8dc3</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:a3e19d59275c21381245500e0c6402eb9b94e662</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:a734bf06ff3062788a0bc2d248734c12dbe9e6a0</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:a86e6295b382e0533813f2cf18fa3ad6ce48fd99</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:ab00f3b97506c3f20b8810a75a1b642941dbca09</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:ab5e1d15a9e8c96a38241af208e888273c2b631e</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:ab890b0ac98097912380a356e0d6c3dda6cbabcf</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:ac8765f3d849013c47e5f5eecc500521abd20949</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:ad2705d2f8ff7341dd4856394f3cf581bcacd965</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:99cfd0bab948e7842cf3750022bfbc17690f782e</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:540c3bac4a5d994df7c78199b27f95e051009f43</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4e68d188e0a1c189dbe80baa4c6e1316c07d342b</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c98b4c40fb403a582c0a585e647844e8d8d9bf26</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:dfd5d872748b656baf7625ffb550eb51c4d60343</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:ceba2fc064f3cb8b208f45770b55122328c46f7c</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5363dd3b52a5d8f0f7a7d203a4983c53c97c9127</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:79aae588dbe10b93eb01ab5aac337701a6a221cd</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3d6899bfd3896ac4bf8411285e3bc017b524c287</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:03338bf9bbc1a3b50bd9e4caf6a82a44b2eab02f</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3bccd9072e854a527b99559015d225c6574ac65e</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:fb941dde99943c273f6909bf70b8f8b497e7e793</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4622498768ffbd024c038a8510dff07e8ba628bf</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:34e4feb8de16ff59994dbebf13489104bb92564e</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f7d599413c058bdf774ad70894ebf64aa2b29017</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3626f4e1d97670ad23e7f5366c140a837344c588</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5508187f440482f942bc712187eadf53729c2a81</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4900e60da18a664f5b6fb90af1cd3c2f8cf5233c</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:afc4af08a5547ac761adaccd32c5cb2b5a1f2a80</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:aff7d66de2b821687eb956b82d72c2dc166c5c05</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:b1faadf974aa10bf7be57281c316f03af4fc4b54</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:b27d8f05b4aaad3bdb352b41d83cb27c13879a87</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:b36c3125bd36c9d24b173b417cff976b5275eda3</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:b3ce44b80041d9934799bcecb62449342f953ef1</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:b45b42848fb60489141864e9f54acc1de069ca39</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:b462ca4bcbcc4cf7a9a25f688f3ca9effb86a400</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:b6afcf716adfdc15a6cf1ebeea2ef72c48c2f679</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:d0c60bf5f8be81447e7f1b3e7b0c3bc4254acd2f</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:cde436cb7e6b9b6b14446d4386951d184525ae2f</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:a488783a9b40ed6a6a7bd02d3759643e5e29dfe0</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:9918ca36ecb1297a066fb98d42541106e616611c</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:9084776819abf03fa5351db3979031986d5c1bb1</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:ca557363960d3cec4c33435ce08853b754cc499f</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:d1163156e60c615eadca96dd76d514d3df5eaf77</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:38bca2173265e59296e67ca0f15351533e7a8538</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:9af59e31580b0dedcbab79e8065e77b68bf61741</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0a63f03274f6d80c5ffe452a915531d86fc6fc98</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3fae88685849b17207ab9939b207a6aad5daaf17</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0932f717a4469522d790640eff0635331e0c419f</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5ef1847f99aba5e7b7d9ee4a2bbd5cf3652b5bb1</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:ce0e699278c819163cf1ddc2a2567b1a6dce0b52</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3e8820608a8765cb835027416456fc418036c878</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:ff1fb71d62ee067a329c488db0593b6de7e37062</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5691a839f50672ebc3269b259221050656cae644</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:cf43cb4f4dfcc47bb458d00262634e1fc97719a8</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0022f4fd78b0cfeb0fb5e258d8695131e0e4bd30</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4877ab43888dc2584fd85788b6b656aac6228a5d</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:ea4154e455a872fdbabf60942baedefd0f0dd42d</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:35b5d0206d908042034ec743c8dce814018c193d</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:449d2891a711a34791392f1de295481d103d46e9</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:9aca7914823794e2790e37302e9aad2b62986db2</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3289c9923215c782762ec9f2e872deebefe7477a</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:fb47e5d4e5ebbd0a42610aef5b5176551dac5324</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f65e0e823686983721c45fbd54ee9fe096d6ed05</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0ebe564bc742d3b241943a3545aae8e0217017d4</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:26f10d98dfd337c50462f665e6603091c30a55c9</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0e50e4fde700ec9da2dd58ab44d1999df6ddefb1</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0dc4b852582702a133981fcc8033810eeab7302a</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:cf54437de488cdeb33642177022d544d838281cc</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0edd315d218eb5fd2866ea194116361d85e0923a</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:29a9923601b5525982c06f20dd6a1181d0857bdd</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:fb014b46c8cf68a109c277f2c114e3e8de0df420</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:455eb4cf6986dda4628d318476eec0374c96eb20</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:047352356cc0f78a8e7f26204ae74013bd0527be</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:455676da549e42cf23d3832eb510c0fe93a5d302</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:09f0ec736e8af488a1cf40df706b29a248285c12</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2f3ecb24cbc20d5597d15e0da835ecc7ca0ac81b</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:d13f1183ab44e5c597f69f08634ab51579cc0e08</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:b7efbd26c61bf192d2d9e05206b4825bc04e35bf</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:b8395cd827c0b3f8583289f20bead9001d001f21</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:b853242b87757431d0d00ef7fcab7d961096209e</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:b93bef28dd17181fb086a243de3c9c19c4a42eb9</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:bbd3d9a99996e95306b3f3036479b2d6931347a9</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:bca6488b541203fa16b30addcf1b8d0993521831</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:be538316d9c3bbdbd06f099fea0d2260ddf42fc1</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c2bb63120499ab718a5f0458f1f4ffd0e181f9d5</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:cffc99469169b65d81ea805740cb7453013c2853</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f7fd72111a57bab31dbdc603d1ea0ad70d02426e</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2a13acdd4ffed03ea1e9bc0dbb480c561f4d94d3</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:1003fee38d17be8351ad808328cfbf63beb588b1</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f73f576de5a5b8863b14dc77ff1b34a72c05ea3d</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0f53a1354c10b1a6d9bf2d67ac85a436f03f7b43</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0a608acec5a7f68b129a1e563346eff84a4398cc</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3f2b940f9bee594cc215d70aa46af17a8427bdf9</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:74be276bd77f1d620be630bc100e1fa9f081b67f</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c555122f2be1791cc45010311e7c36c82f7f9de4</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0a51f89d3e293835155157cf9f9e12c5005d4396</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4f471a1a02d40cd7e3261055af5075490f7d18e9</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5970b70b93261f4a875dffb4f783b6eb369f6906</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f5c7f31aa780c341f69351a3a6e2b1c381c74de3</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c71682647995cd6285cc8b916c1673da2aa16714</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3d25efc978e327a15e7812ae587205b4d5cbb0aa</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3f487516399a8062ce295be08ce5af9ec7bec940</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:9f30e99be9912fb4e73a8f1f82d15917658fffc6</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0bc129a2117b5b9eb266266df13f7c892754f883</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:7e2f013af1de67a229ce0ffbee376c198837e5f7</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:103fdf30b18ccae3dc9200a2f0b6c5a8189a5aa2</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:49d3650015f1772778f6f37ffa2e25fcf1ffbe66</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:510c24c86978cb9c2b4c07f09fa5d4d4e6734e65</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:45f2355fe5d763d2b352d22c98754918a38fbe11</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0c328baa77b2bed3e45619fab797a5d57664758d</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:7c3d6b4610dc7da7fc0d59ed8c4c50d5ff412bce</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f4e3c85f6a542be3ee4dffccdaf6e17749177996</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5c6d19fd23030dbcac5c65180f73c3fc88b9e9eb</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f80a3dcabd716307d146a196888ccb10fd813841</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c703f6aa29d66f72b313cf1d76e2bddd0e7e0cf4</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:327dbd4a35c2036bfe0ad719274994411e383546</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:40710c24dbfa09447d45952236bf3a799a0c3080</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:49f93c56314b599a02f5e3ad956b9fe756a1f0d6</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3c4aaf96ee364863d855451dfbfda38992362e02</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:fa22d320c08c1f14ad5741062f6b16224febfdcf</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f43b4444b4e4601548de84d3123f160b51f934c1</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0fcfcae9e5d311de42451c0783dd274b7b71d810</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:47ac0e3a00f2705a44a7e3d08b25b0c1fb489a32</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:59a5ce0c414d51824568c8e0dbf4fd815f61da0d</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3a620c8f466d217da42990425b82b6102c2ebbbb</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2fba16066c88d49ce2b057c1b0d51aa40955e20d</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f46e14f3bb142169f8b79a465485a1de28699447</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:32209b33f29bc0a88a28ae98580956fa571285b1</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3bcf10784a3d9a68bda8b3bae50c5f25ad0b7f7a</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f52b2ffbd2ef478fe56b55bf3acdb8948485a8ed</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:39d05c10c7c4b839b50601c1fff85a8a5ce15538</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f4abbf74ca074f7bb9f77669c6937d2e91c01414</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5302423800f33b4e05b09c4272d0f9dcac3da1c0</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:441b6b05f9244782ccb215a6d3185b3657d4a390</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:d1bd5b02e39081f922a677275d4893fbda5771cb</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:41ff32a03e45bc510bcd91405257fe844c8e74b7</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2ce6b120675b7e1d262f34cc0be9b95815698c92</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c407a20abf620547f3f8d6bb49d339c212ef99e2</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c49dd478b5a7cafda4a46dbebb9e6d3d5efe1963</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c542961d6cc3c663e755d26a46dcdf640d2ce852</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3f7c5c567b22133c5da901b887e551c44a72d8dd</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:065337f73cdb8671e1aec0ba2c2d0a97c3dbe486</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c84daf17da1fd06f7156117bcfa1748ae2df75bd</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5006581550ba669f0dca45cf001d353017da4d35</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4eebd096a05143474fd43e34e51d1fcfc4843480</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c49659a8fe79e2f434dd14e4ce46a7afb92d9a96</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:fcdb1d2a30d373a71392382bac2a92ff22590c84</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c47b026d8d26b04d130a226d3fb8ed029fa0274d</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:7ed55d027d6817c6df46e09dcacc64ac1680bbf0</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:50b081379c9ab95000721b085a70dd4852e6362a</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5113158c8b21d5fab06345f2d93c605376036701</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:31bf98cd45ca123e54d7ee9118ab48c86f151947</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5c1a42cb0ee077554ed267e0dd5070b65c7376ec</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:86d5834311dadd713e2522ecd18283d607630b92</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2a86b113717d626d7c7999d9c0a32f9c8bd2757f</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:cd8e6d3818f93a4f4186eed0ebb91bf674c7fdc0</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:33c36905aee1c39df270c7f316ad76708cb9698d</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:fd84ff8e09eb50ba35cf3e67ad0e2960bba7aece</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4550163ff4454a5d316ff16e6c63479efff977fa</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:30045968ff8830865c90952137aeca0f85bd15d1</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f5cd2e81ce640278a7c02f661075bf868f93f5d5</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4de37babadb83d8886287c30fbd754668cdf79ac</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:ceb37c6b9a24c89a983af0a9310bba5d30ba0f3b</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0ed343cb2dc343c68b8e9496db52b77245ae4d85</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2a6f9019a4946de25cad8ebeab817377cec88bd7</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c4b9838c8730631521fd6c33615efaf2a8e586eb</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:024e0bf9b58a3af78016de51190e78f2e074a859</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0268f40a5228e78fd06b07186e335f166d8dc970</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f6774f9c2d58089cc8add3eb2bf0d4ef9bf1a4a8</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:381f1a69017c83bdb8e97b6fe127d88e4786a782</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0e2a6aee97bfd64f76a2fa20a0bdfa789c9824ba</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2992323377dc4450df40d862ebac5736ac5908f2</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:ca570d2eb025e6faaf3824f129d3f629eee22632</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c9cba7a3e4bab3cac1d5f569ed48cd9c3ff4ad2a</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:425a6ecdac967d4c959fd306daf2465062c183ce</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:ae1ab56368e6fe091a3926f778c915a7566a9ddf</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:cfc53a9c86988373b4b9947db88e36f3d273afb7</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0dcea6e87c651bdff7d7a55e23a758204e8b23d9</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:fdfb60287ec964c4c3adff0871e4110c46ec4b22</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:46723468b4ac5d41b88b59a6aa1f736004772209</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f5a76014ba9fa5eee52c7bb624d9d7b879a1666a</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4833b57bd5bcd046192b7b1452ebaa054479a61e</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:491285cc1b46d784e183f822e5cc0d576d83dcd5</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:15b71fe883d504a19b5bf959082dff9f84d1e721</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0aadadffaf0181378a538cb86a4f773398cd3091</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:ccd6076bf90f8d7fa3d7a8b71885c6b15dff3438</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:cdb4bd3b3d970f84133e1a7ee060763c4f40d07b</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:47ca66153f08ccd82ac9d0fb57ae841152151c9b</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3e500c3b42eb36e9fbdb24c83c2c52831cbdf04b</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:1516e3b07f2bc4f3fbcb62ba426861b4dd5ac9ce</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3867dff8dad4b8c32eb14177d5d43c09fa75679d</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:d00d7b83837f2a249cdc2237e900c92a147b79e9</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:8ec22bb584565f0b7bb6dabf556a4117b8d3a161</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c998e682d1b8c8f4e90d1f02b63585e6c008a793</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:275614711c1680e6a6cc3f818c26931754101c83</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:e8c92644623df31f1242e91d3911d1abb4612994</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:70e21feffface22e553da1b1ea1367360474373d</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c62283381109d9222c2e14d7eb1695926804a8de</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f4b482378f65e41de27d1a78f7ea19a26d8877ac</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2b157b603793d949c450a9ee8e91d0c0124a4bc6</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:344f5f7f52707434a9a536230ec576ae0dcb3259</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2de6197247bafe12bc4d9567321a14e8fe2cd694</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:39911dabb9996cf3a964a6f86b9cb41e227f0490</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4d0959fe56327ce042b34df33ca9768edc5c025b</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:baf1d84bd820deac30b979e3d0092359f09c46ca</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:d0be9cd0f4c68528ff630399f3e5d48c7ea75f14</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:e8cf891f886f895d52317b06a05449bad1c02761</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4aad64e1d0ea7e6a6c1919845788fad7a9adc0e9</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:05be6650930dc44244da9ff95aff38e489569268</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:05bb15fa2414e81a43aa6cc8daba181d6a136e7d</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:de2c38d7fae83de8ed6a2bceb44c0634fbcf018c</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2e46a07125fae002bbbaf8b088f2aad706af54b2</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:36811ded304b033d4fa872f1703f8b97b6deef3c</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:8af2a45f1f9a8b5cd9bfa8765c31fbd5343e19c8</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:fdc32f74c3cdeb01504aaa8231f66a374bd6c743</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:9bac98d0062eb28e9233f2a1f3b85346b487588f</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:7b29314957053e8cbcaa4b33ec3bea95d8ee68bf</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:744148b85dd0e688c0a95350bcdf590135a5941c</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:106b3fb918774409973272e26b06771d50b2fca1</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:fc2cebc430eea65d487499c672f878cf8303a385</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0e84be3e6907d08ae600a0b5e0c73c5d255535d0</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4b5de02993751e090c2195dd400e71c0559fd630</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c4512ce4a836521819408edc2921edb8bd3d4a0a</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c8e796cc30530127dd33e38a8f751d91b9e7046f</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c947187c008e1aa42bce120520d9a73bd901c84f</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:ca0c7a79f00bd6905a2ecf2026cbc5d36b82dbbe</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:ca6355904f608e13f0184fc09e1f6d5a45a70d75</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:cbffaf22498e8283deee12e8fba15986e5491ea4</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:cca9a00c38af4d1cff758b89582d6b030585000d</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:cd6124ad8ab92e1107268f3b627297608ae3b0aa</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:d020d10cd163df96711747d4ca009ba0adcb1aeb</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:d0367b241e574b35a485bfb42819e6257fbc9711</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:d07dda854210acbf2014583084355dabad7b037a</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:d0e9a4adf36af9d0f1232b587204fa688ca92dbd</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:d12e4e3ce00c3a70fb650ac5f4df81b6cff56c8a</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:d3778e6dd418c00fd64d7e6937a6611aa609bc47</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f41a123707579853eedff2a6ec6b1e1c2a6188f2</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f8658f6be7e03d1c2fb128fb8affd181d8d618c8</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:381008518531f686350689426c3a53e258bc74ae</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:334f354cc2c4f69d81423b671bc41c04201041f3</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:47d36b854a178435c9751ba48e718dc12c5bb353</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2924dba94e220200a5f63d9d3ec8087b023e75a5</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:d3b2eb07f9b9fd406b28789a3ef531a2ae9165d8</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5085b45d9bbe2c0017058981a0a9621c7bb485b8</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:966852a8196e1c58c39a7192ce4556fd31e66b8b</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:ec1782687a25ba5e2d9d2180be4409b1b04601f7</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:e03ea25d95b9fa0b79e2721c4398abb8c9715467</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:fbe5ea567a8cf7ec8021c3e6b77bccfcfad2240e</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:67ae779184233795179e5e823412c8e7272c7016</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:062a571a088a1f9bc3a0aa80daccd1267ed3fb2e</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:80e45fc578a8ab3d75b2aaa5a91f5c43fe953876</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:61e046244ec33e4f2488e5913fcff1d7db526e52</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3a377a784035073ca5878456e58aaf11004943d8</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:02f976ad49b6c98f3b120b6b09b3c15611353677</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:d46ef74bf3ba99a75d3a508e4ca06df4fb43b966</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:d5cb2dad1d4558896622a97bf888c69fb18d6453</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:d6deb36bcaa529ea8c0f27143524bfa88c383cf1</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:d6f33ca5ca9acf64101c2cc7f5b01952e8deb266</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:da405c51b85183f60ba2f1d511bce584c701b675</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:da457d5790a4456acd566e3ac9e95caf26d706b2</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:da5e8af75c21d8d0608351682af0503f2fad2061</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:dac237cdccb249df4feb991151f2cdb6ce472eff</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:dbab88e5090a82a99c3e9611868aa6d284cae170</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:58302fa635bf85323c000825b4e520349d5ece5f</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f6090910560340032a77698dd74a2a9d0d904d25</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5e6f653b9312b437d4460087be03eafd91685b9b</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:1e95a8c7adf2b71bd5f2907926f265a960b1da98</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f96733e907ef33eaa4cef47ac4a59e94c5d3c345</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3fcb639ee221dff21b57f4eb50a5d401d482bf7b</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:157f203c418408ad71bdd058b98876e8ab627b1a</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2de9a24defc87ea3f04ff49285bc966d6a631e05</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:de7d02d14460aafe155401a397f1e1fd936798d6</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:decaf5b702f9182eb49c3ceb2a0c861626dbf6a9</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:e017d7c4f4ce89c9efd59b9d4c7e8447dc198007</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:e0cf339a095075498b3faa6e4cc2b642456e566f</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:e2e40cdf59f2a8c71200b0d41385215cfd73c611</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:e455340ee6f4f28e737b96345d9f3f852ed2a07b</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:e6d550ec55d13d196d273c07a17c3ad11e823e6a</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:519acafa0aca69fceb6c0108b12a3152617e480b</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:107bbbdbd9a5db5ec35ee4cd64519e0ed53b6a8f</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3d360088bcc9a40f2741a61b3a6f8e62b3e2a339</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:08a49b4f8c59c8e878ca93ba9ce57fe8d5c18852</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:26a2bb308c7a164b80413cd83b3e723f6a9adf69</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:1d95d91a34867febbe8b4026e7c8ee7e92d4b174</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:034e31b64cd5c7a52685ddf9cd03bc86aab44b3d</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:389ed1c1db2a49faab71c2487b9d0aa8e153f5dd</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:015b3d2513f4fc7bbd03ec2ea1a039613f110202</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:27b37dcab66a44c71b662f185f1a6c567706a8a7</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:329e3c5d5a91997ac49afa02e4980b7f8f593169</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:fd9b93e87f06503b53899fbcb79c2c3cc464439b</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:025e521318d7bd3725a7c68dec60149fa12fc204</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0a9c926e8ced4fab8f1b9c6a754ae518579f14d2</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:cfa6180a2351b4bdcefa31ec2b245858623aa54c</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:1c1575e19bb7eac63127ac621f58e52e24bcbcc0</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:e9481fbd5d45cd7a9681a23b29e55b3a166acf38</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:e98c4d5cb0c2534b8540cad529626965904f2457</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:e98eef21c25f63bcc6c38e2741032c4d64de7d6c</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:e9d92dac28d340b375d9d3597c873f02bfc2ecca</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:ebcb546a8aa1bf09e01e77077120f4db84ae37a0</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:efc27c7ffd7e8de5272203e835c4dc3cc064156c</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:acc3dbf5e1728e6b3c9cabe9bb3eb95c2f6dfbd6</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4b092c7bf475e0d9b07e13f9aea9972350d9631d</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:10dfd400d918c94d270cc26d21edde2eb148aed5</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5640e350c0f52db6d16170b9a7c6c29477473b05</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2875ddf0127f5198e9bb8c9833bb658a2f109484</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:28b88841c7b50e6f053a700849f96e75450c8a1e</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:28bd1fe1ea477ed9bd8c66755250b3d945a5c0d3</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2a13b1102419595bfc9f83389933a7897a49eaec</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2a291ed458543ffcadcd6a211dad717f7db053f0</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2a7ffefcaab9114c1fc7c567eabb98a796f1c064</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2b1e48b389b7ab42e54ed8de2c7d06d9981e0c6e</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2b24759a952e2c9090bc8269e8370f63b9655434</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2b5c4622d1523e1c4b50a8c68e52abecf98a242f</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2b66aba812c846c251bcba4edd750cc91ff0195e</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2bcdd210a5ba6c75e0b9b617bee722cd27158cc3</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2ce0fa8fc53bed2fa597413af9a2146a29e06ee3</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2d9ef73b7d497057d4122e58d532a0106cf7d2cd</t>
+    <t>magnet:?xt=urn:btih:ffd7d26a7ab0757539979105188eb3d1abcd42c0</t>
   </si>
   <si>
     <t>magnet:?xt=urn:btih:fff0f872f7467ae278af30330606b994f68ea328</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f63f12f51a99471b7a53084ef328ebcaca511372</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:50833bc0dfbf04b37b08618cc2f36e176386ecc5</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2f303d9692099bcabc4f9afd562317a2ef8f3768</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:683fa20e90eb6049ff55a9eed378c805d86572f0</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:310e26463b6129d13b4bda260fa968b36a6b6e69</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:9c36b49ef0acc43b9797f00aad1294f7d930f8cd</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4904be0062046e14ee694074b2e98058ea4673c9</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:cdd8a740ae681f6ed501d50557d37b2ac31715d6</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:6032602dc5523fdfbda52ce2d6df677a116b5518</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:071fc1c5cdc352c8b440fe6e107d9c072febbb98</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f73f3045b59b32fdb5905a7233619c6fd9617cd3</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f4f8b5e88d07f3c20ee67a9dbdc81328d72d38a9</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f61d60e34313947b9060c26bfd1b72719806a734</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f6e585331210a6c7ca4c6104779e5f111804087d</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f85843931dc0edd4dc6ed19b105ce743a9d53a5f</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f8d4f474d0cea4de07dc1688488318da9858d750</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f9935dab79ce2e0ea186db9e4cc742670020d497</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f9f6fb9d1ced8e7217c5d9cbc9feaea13f38e1ee</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:fa38383a1ce94cac44e0e13bc61624532f0e091e</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2e53402e6178768ab939fea2e5fe7e10bac64f89</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2e55a688919894fdeaec627e97631220f15079ea</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2edf5fb67444dafe4ddd842572e6ea4c48457ba5</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2f3378bc54b8990e322d9f089a4327d40044546d</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:319e2203589731baab8ac2966f6b974492ac8990</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:359c79fc4e7960a6ff20b9e75491f2cb017d5f77</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:35f1c3564b4108d4e43f081927f3360fa84ed13a</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3657fc474ba25a41538f989cb3b2a2680288f2f9</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:367fc91c2d1965509a1b762f408f3164060bbd40</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:37400da692adc40e6445360dd39cb23b45e0f724</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:385df497fd6c4fc0a110ea037878b37371654c7c</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:fa2d7071cae55142eef04c5fd7dd458a19a18ede</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2842e83c6978bf4c8b93665fd0c4db5f61c7c5bf</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0f91e1e1b5e60e983874c900045d3c421d440b64</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:06d70a00e24b4981cf00755e183e5f17104788df</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:522edd9df0ead16d7ad89a0cf84ef9e009d2a551</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4a8df1fbcf06dc53a5aa7296a0b12966d9c8f3a0</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:fc68367ab28a5eb10871c7f2a3ae59d1ec2f3f7f</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:68ec50623929d1e305e2fa1caa1d9bda5b05ec27</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:e04af24fa4840e3a0d08427b524ce767ea0d43a8</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0912b9d421a5dce44b5fa8716be1091f5afe0492</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:10ff4926d4dc5371166e5850322d1208a54ba587</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:59d46454c43a73e7b6e624df7531010a77b5b6ba</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:dd6cd8ffbc272ceb70284b98610b3fa08fd99d4c</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:dc2c7d3bca2b10cb5a5f588307c4d6becc6a6e89</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c690e376b3cf5a6ed406b17e23ddfc3fc15e785c</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:fcb406e769f52e680de44ff1e6eae5510160e722</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:fd04b726dc730e813734a5d40f565d7033ce6ffb</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:ff7687399bc5f83ba185bbcfcabb04ef38e99b6b</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:005e1a46ce649ff9d864902bc13e82f38177196e</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0070df3803321c001ea82a5b5f08311f19dde3b7</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:00e6630acd508efce45927913942da8ef22c6b23</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:00f2c68a326574af10a9dc89bd6686ee2bff0729</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:01d13893ea3b1d6ce4ec84651f56f479d8771c6c</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:02bc27944279b7d2a91065d006d63c2bd44eb332</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0370aadc9a913f6cef9d3c6835cfc794dbefcd17</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:04df81cbc831932cf09ff67f29aa3e313d0bc363</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:05d3cc005ebce5da93b0bfd944e7e79a1285f198</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0633d4b8cddcbef337e9c749645e00dabe815127</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0635d9430084aa01edc4ddea5e8646010e5ca2a4</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0642112cb96239e3ddb7c9fb615ae3a2f52291f9</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:06e8b95b472cc866c2f6dbe94e94a7fcb0ca8765</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0744b67c4ce3077dc1b1f8dd35179cd2bfcdb979</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:076c8dd9276fdfe165a1f776b7785b21778366a0</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:082d2353069a2a16d8b00830febca425dc440d9e</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:086ccebbb9b9d17e43ca24dcb8ada5138ff96878</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3a304a3e0c8aa200ef8cd6ceda3d1b438440c5e8</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3a3f522e18f124fb8cac7ad3e2e34f3c3700d18d</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3afb161dc63c30719299277ea5ca4655a7d5ca5a</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3b21adad00dd4c119301251225510e60a11d5ce6</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3bdd3650c63f8c4ef16086f5ae0db89301879e8c</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3c3952bb88f69afbd8dbb7fb07b2d2d22b46436d</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3c8013e00e861f06c9f07e698ccddc58f8515abf</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3cccd8a10aa858e2bea076eeae90ddb1932092b3</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3cdbb0e4cae8949514dd32e517c9c9a04927b5f2</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3d185e21717268d9019fe5a0c6dda79a39116a38</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3e1ff29e4148e5a1e6cfd85ad434f20b8c6e9f23</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3feedbc7dd44b821aa558f9c122c612ba16d15aa</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:406df4a09e836a3c9f4425417add44d8c5b152ed</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:40bd6a69c04b8a318a9ea70b426e283a40d3d382</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:40c9d241c5c051b388325401cc8626ca60915b42</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4162167576eb38e65b8fe25d5d71430bae1c2bad</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:420971b77d66d2244047fe8c6907d2da60eafb2f</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:42b0f8b865a504ef1882a9aeb3c37ec4b77fba86</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:76c83d31a76321194386a9f6188ad1753f175078</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:59e5addd5c52e6ca0e3da115c802da6acb9be84c</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2fd1f9834de9773eafaa893dfc6e76665f6eaa92</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c9e52feedcebb1aa344c5f71ca2aedd8ec282b82</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3530f80d0eddf06cce6e5a93414c6b9e1f62337a</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2a25daf97898d7c70a9803a0e45defb2efd34953</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0210b42faedba103a73f5882871633a7742ba471</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0ad1bd126836f2b6be7c45f0d568acad209f0127</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:25ff03c5c5c052fe8d0f0d0a3f93477da9d8d1d8</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0128f5a710ceb3384831b79f3829d061ac2ea595</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2710e82fdbadbd99e20b8883b65aee53981fef25</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0ca37652b005f83203686f08ad760914cbbc4d8f</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:39f21b69486a8020a4525746fb0123198f7cf588</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:6f9c8f85ed248b5468ce7bd62dd967d6eeb95689</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:ffd7d26a7ab0757539979105188eb3d1abcd42c0</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:34c8f835be534c0a1e041cc95cde0bba4806a532</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4050143600e2f97086d2bd7efa9cc9f3c8e87186</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5757479b4b410d228fbe873557dbe08128690ea2</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:85c6fcd29109445a6f114a461098f6fc0fd7e423</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:08ae74cf35679162763b5994b05e71906df9ea86</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:08b8fd34f5f3df3a252aeeb1ad0e8ab614aa32d0</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:09483e3a016488264ee3f1fedae8ac7451333bf6</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:09573e048348dee6a28a7d169542e53bd54cc0af</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:09b9020cd5e81e0f998d02a717fd7f198fbf50be</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:09ceae5b84ecebc8db45f2b0f71adc507a7bafc8</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:09d20552f114f79f2deef467f8f4090db0e89333</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:09eed306baf98d0a58c05fb6320f0c76131f5e84</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0abcac298c335d7a291c422beac07251a790bc3b</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0ad1e33c806c92a5ec17347aa7558bab0e71aa45</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0ae58f21e5f56727964056e03f1e1ea9c0e61ec7</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0b8eeae0b1f790b25af6227aecdc412cd9329f87</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0bb5b1cfd7f71c0bf290fd5a03e0cd7603c24623</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0bef9c14f2639ce3742a3c660cf9028bf24e22ac</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0c16afd19ed718685ca87bb9656a879f1a15cb65</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0c6abc76b8685f85a6d20a4e0b335c0153217c1b</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0c833b000d943c5634d33c5fed098a02fe3fa4e5</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0caead9bc391e61f1c2fc24a5d1cf2c06b378251</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0caf811cc3fcda18f13cb65d383509512fd32282</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0cb877410b647de6dd904db41c6e62d2e1c38cf2</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0d562ecc1b6ce629cc3c418dc45c3c200d4b3be0</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0e3afa3d130f020bf3c51d1aa6104ef984f1b0aa</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0e573fc6e0b93540054630193851deb560100520</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0ec2acf9e1f3a4194fd7f2979f624a40f9abe8f1</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0f986ee60a84b065a2a18e10088e77f53efa0610</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:1081facce69e7bfe861e184f4225c34f445b910b</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:150cd32cab4ff2764a1d0b29164d7811a5c357f2</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:179ea8518ae7048c4a838b0b2abf0ad3444f7c69</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:17fa2db37cf7d1583e82318fba96fc235db575fd</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:191e7a47e210937236087187904c524e838270d5</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:21f9acb1190a3b1dd48da7938de87463c10ad0f7</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2378bf11f2049d4f8180bea9195990031ed9bc0e</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:26625128e935ce560b88233bdcb367f2becb06cb</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:269f532962e82f7f033fb5d13caff88789e2cecf</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:26ef9f4297da334d763d63f24065f48fb723edb1</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2747436a22b61d0737a8abe403316344e2007abf</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:280ca4788e226bb6ada4b8d609d9a36cd7bb9872</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:29745c41b214aa32aab9f0725e5dc543423cdb23</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2a272caad02d80b8999ea25fafbf2adb4c170e16</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2a56a349215f117543a5805302d41a6473889450</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2a700ee8034d4579fcce4484a1d8754d95558689</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2acccda5bf669e66f4b60dc2a59aa6ca8a08daa1</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2beeb2950b8edd998df0774cdfe379009ad92f3c</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2c385bb43839fb7044d1d6db5714cb1f99d04e20</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2d0624ab8c1f3f216012173e6b8092cd9cff53fe</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2d4b90318507de9d3d37fb4f00a0ade58b4d8316</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2ebfa0a11b91327cafcde1e79f41fb89583de9e0</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2f529f7577ac6fb258efe8cc6c197676dbe9f8a4</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3099ca9b94ddd935b42abf69018ec5cea9473330</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:31a2c4fadc48399d3f60954e646e3b71ade91085</t>
   </si>
 </sst>
 </file>
@@ -4093,6 +3910,13 @@
 </styleSheet>
 </file>
 
+<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
+<customStorage xmlns="https://web.wps.cn/et/2018/main">
+  <book/>
+  <sheets/>
+</customStorage>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
   <a:themeElements>
@@ -4343,7 +4167,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:E1053"/>
+  <dimension ref="A1:E992"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="67.125" customWidth="1"/>
@@ -4366,77 +4190,77 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:1">
       <c r="A2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:1">
       <c r="A3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:1">
       <c r="A4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:1">
       <c r="A6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:1">
       <c r="A7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:1">
       <c r="A8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:1">
       <c r="A9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:1">
       <c r="A10" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:1">
       <c r="A11" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:1">
       <c r="A12" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:1">
       <c r="A13" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:1">
       <c r="A14" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:1">
       <c r="A15" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:1">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -9319,311 +9143,6 @@
     <row r="992" spans="1:1">
       <c r="A992" t="s">
         <v>995</v>
-      </c>
-    </row>
-    <row r="993" spans="1:1">
-      <c r="A993" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="994" spans="1:1">
-      <c r="A994" t="s">
-        <v>997</v>
-      </c>
-    </row>
-    <row r="995" spans="1:1">
-      <c r="A995" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="996" spans="1:1">
-      <c r="A996" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="997" spans="1:1">
-      <c r="A997" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="998" spans="1:1">
-      <c r="A998" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="999" spans="1:1">
-      <c r="A999" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="1000" spans="1:1">
-      <c r="A1000" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="1001" spans="1:1">
-      <c r="A1001" t="s">
-        <v>1004</v>
-      </c>
-    </row>
-    <row r="1002" spans="1:1">
-      <c r="A1002" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="1003" spans="1:1">
-      <c r="A1003" t="s">
-        <v>1006</v>
-      </c>
-    </row>
-    <row r="1004" spans="1:1">
-      <c r="A1004" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="1005" spans="1:1">
-      <c r="A1005" t="s">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="1006" spans="1:1">
-      <c r="A1006" t="s">
-        <v>1009</v>
-      </c>
-    </row>
-    <row r="1007" spans="1:1">
-      <c r="A1007" t="s">
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="1008" spans="1:1">
-      <c r="A1008" t="s">
-        <v>1011</v>
-      </c>
-    </row>
-    <row r="1009" spans="1:1">
-      <c r="A1009" t="s">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="1010" spans="1:1">
-      <c r="A1010" t="s">
-        <v>1013</v>
-      </c>
-    </row>
-    <row r="1011" spans="1:1">
-      <c r="A1011" t="s">
-        <v>1014</v>
-      </c>
-    </row>
-    <row r="1012" spans="1:1">
-      <c r="A1012" t="s">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="1013" spans="1:1">
-      <c r="A1013" t="s">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="1014" spans="1:1">
-      <c r="A1014" t="s">
-        <v>1017</v>
-      </c>
-    </row>
-    <row r="1015" spans="1:1">
-      <c r="A1015" t="s">
-        <v>1018</v>
-      </c>
-    </row>
-    <row r="1016" spans="1:1">
-      <c r="A1016" t="s">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="1017" spans="1:1">
-      <c r="A1017" t="s">
-        <v>1020</v>
-      </c>
-    </row>
-    <row r="1018" spans="1:1">
-      <c r="A1018" t="s">
-        <v>1021</v>
-      </c>
-    </row>
-    <row r="1019" spans="1:1">
-      <c r="A1019" t="s">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="1020" spans="1:1">
-      <c r="A1020" t="s">
-        <v>1023</v>
-      </c>
-    </row>
-    <row r="1021" spans="1:1">
-      <c r="A1021" t="s">
-        <v>1024</v>
-      </c>
-    </row>
-    <row r="1022" spans="1:1">
-      <c r="A1022" t="s">
-        <v>1025</v>
-      </c>
-    </row>
-    <row r="1023" spans="1:1">
-      <c r="A1023" t="s">
-        <v>1026</v>
-      </c>
-    </row>
-    <row r="1024" spans="1:1">
-      <c r="A1024" t="s">
-        <v>1027</v>
-      </c>
-    </row>
-    <row r="1025" spans="1:1">
-      <c r="A1025" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="1026" spans="1:1">
-      <c r="A1026" t="s">
-        <v>1029</v>
-      </c>
-    </row>
-    <row r="1027" spans="1:1">
-      <c r="A1027" t="s">
-        <v>1030</v>
-      </c>
-    </row>
-    <row r="1028" spans="1:1">
-      <c r="A1028" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="1029" spans="1:1">
-      <c r="A1029" t="s">
-        <v>1032</v>
-      </c>
-    </row>
-    <row r="1030" spans="1:1">
-      <c r="A1030" t="s">
-        <v>1033</v>
-      </c>
-    </row>
-    <row r="1031" spans="1:1">
-      <c r="A1031" t="s">
-        <v>1034</v>
-      </c>
-    </row>
-    <row r="1032" spans="1:1">
-      <c r="A1032" t="s">
-        <v>1035</v>
-      </c>
-    </row>
-    <row r="1033" spans="1:1">
-      <c r="A1033" t="s">
-        <v>1036</v>
-      </c>
-    </row>
-    <row r="1034" spans="1:1">
-      <c r="A1034" t="s">
-        <v>1037</v>
-      </c>
-    </row>
-    <row r="1035" spans="1:1">
-      <c r="A1035" t="s">
-        <v>1038</v>
-      </c>
-    </row>
-    <row r="1036" spans="1:1">
-      <c r="A1036" t="s">
-        <v>1039</v>
-      </c>
-    </row>
-    <row r="1037" spans="1:1">
-      <c r="A1037" t="s">
-        <v>1040</v>
-      </c>
-    </row>
-    <row r="1038" spans="1:1">
-      <c r="A1038" t="s">
-        <v>1041</v>
-      </c>
-    </row>
-    <row r="1039" spans="1:1">
-      <c r="A1039" t="s">
-        <v>1042</v>
-      </c>
-    </row>
-    <row r="1040" spans="1:1">
-      <c r="A1040" t="s">
-        <v>1043</v>
-      </c>
-    </row>
-    <row r="1041" spans="1:1">
-      <c r="A1041" t="s">
-        <v>1044</v>
-      </c>
-    </row>
-    <row r="1042" spans="1:1">
-      <c r="A1042" t="s">
-        <v>1045</v>
-      </c>
-    </row>
-    <row r="1043" spans="1:1">
-      <c r="A1043" t="s">
-        <v>1046</v>
-      </c>
-    </row>
-    <row r="1044" spans="1:1">
-      <c r="A1044" t="s">
-        <v>1047</v>
-      </c>
-    </row>
-    <row r="1045" spans="1:1">
-      <c r="A1045" t="s">
-        <v>1048</v>
-      </c>
-    </row>
-    <row r="1046" spans="1:1">
-      <c r="A1046" t="s">
-        <v>1049</v>
-      </c>
-    </row>
-    <row r="1047" spans="1:1">
-      <c r="A1047" t="s">
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="1048" spans="1:1">
-      <c r="A1048" t="s">
-        <v>1051</v>
-      </c>
-    </row>
-    <row r="1049" spans="1:1">
-      <c r="A1049" t="s">
-        <v>1052</v>
-      </c>
-    </row>
-    <row r="1050" spans="1:1">
-      <c r="A1050" t="s">
-        <v>1053</v>
-      </c>
-    </row>
-    <row r="1051" spans="1:1">
-      <c r="A1051" t="s">
-        <v>1054</v>
-      </c>
-    </row>
-    <row r="1052" spans="1:1">
-      <c r="A1052" t="s">
-        <v>1055</v>
-      </c>
-    </row>
-    <row r="1053" spans="1:1">
-      <c r="A1053" t="s">
-        <v>1056</v>
       </c>
     </row>
   </sheetData>
